--- a/research/traditional_assets/database/data/peru/peru_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_engineering_construction.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0960105912983225</v>
+        <v>0.09575908505399244</v>
       </c>
       <c r="C2">
-        <v>651.7842384347339</v>
+        <v>646.0213367748346</v>
       </c>
       <c r="D2">
-        <v>462.2842384347339</v>
+        <v>463.3263367748345</v>
       </c>
       <c r="E2">
-        <v>-511.4</v>
+        <v>-504.595</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.805</v>
       </c>
       <c r="G2">
         <v>189.5</v>
@@ -1439,28 +1439,28 @@
         <v>132.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3422915</v>
       </c>
       <c r="N2">
-        <v>132.6</v>
+        <v>132.2577085</v>
       </c>
       <c r="O2">
-        <v>39.117</v>
+        <v>39.01602400750001</v>
       </c>
       <c r="P2">
-        <v>93.48300000000002</v>
+        <v>93.24168449250003</v>
       </c>
       <c r="Q2">
-        <v>120.083</v>
+        <v>119.8416844925</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0960105912983225</v>
+        <v>0.09636815156968934</v>
       </c>
       <c r="T2">
-        <v>0.7767418785034671</v>
+        <v>0.7822732221837191</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>387.3891113276259</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09575908505399244</v>
+        <v>0.09550757880966239</v>
       </c>
       <c r="C3">
-        <v>646.0213367748346</v>
+        <v>640.2631440036339</v>
       </c>
       <c r="D3">
-        <v>463.3263367748345</v>
+        <v>464.3731440036339</v>
       </c>
       <c r="E3">
-        <v>-504.595</v>
+        <v>-497.79</v>
       </c>
       <c r="F3">
-        <v>6.805</v>
+        <v>13.61</v>
       </c>
       <c r="G3">
         <v>189.5</v>
@@ -1521,28 +1521,28 @@
         <v>132.6</v>
       </c>
       <c r="M3">
-        <v>0.3422915</v>
+        <v>0.6845829999999999</v>
       </c>
       <c r="N3">
-        <v>132.2577085</v>
+        <v>131.915417</v>
       </c>
       <c r="O3">
-        <v>39.01602400750001</v>
+        <v>38.915048015</v>
       </c>
       <c r="P3">
-        <v>93.24168449250003</v>
+        <v>93.00036898500002</v>
       </c>
       <c r="Q3">
-        <v>119.8416844925</v>
+        <v>119.600368985</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09636815156968934</v>
+        <v>0.09673300898945142</v>
       </c>
       <c r="T3">
-        <v>0.7822732221837191</v>
+        <v>0.7879174504288742</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>387.3891113276259</v>
+        <v>193.6945556638129</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09550757880966239</v>
+        <v>0.09525607256533233</v>
       </c>
       <c r="C4">
-        <v>640.2631440036339</v>
+        <v>634.5096921102106</v>
       </c>
       <c r="D4">
-        <v>464.3731440036339</v>
+        <v>465.4246921102106</v>
       </c>
       <c r="E4">
-        <v>-497.79</v>
+        <v>-490.985</v>
       </c>
       <c r="F4">
-        <v>13.61</v>
+        <v>20.415</v>
       </c>
       <c r="G4">
         <v>189.5</v>
@@ -1603,28 +1603,28 @@
         <v>132.6</v>
       </c>
       <c r="M4">
-        <v>0.6845829999999999</v>
+        <v>1.0268745</v>
       </c>
       <c r="N4">
-        <v>131.915417</v>
+        <v>131.5731255</v>
       </c>
       <c r="O4">
-        <v>38.915048015</v>
+        <v>38.81407202250001</v>
       </c>
       <c r="P4">
-        <v>93.00036898500002</v>
+        <v>92.75905347750003</v>
       </c>
       <c r="Q4">
-        <v>119.600368985</v>
+        <v>119.3590534775</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09673300898945142</v>
+        <v>0.09710538924261067</v>
       </c>
       <c r="T4">
-        <v>0.7879174504288742</v>
+        <v>0.7936780545141355</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>193.6945556638129</v>
+        <v>129.1297037758753</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09525607256533233</v>
+        <v>0.09500456632100228</v>
       </c>
       <c r="C5">
-        <v>634.5096921102106</v>
+        <v>628.761013374051</v>
       </c>
       <c r="D5">
-        <v>465.4246921102106</v>
+        <v>466.481013374051</v>
       </c>
       <c r="E5">
-        <v>-490.985</v>
+        <v>-484.1799999999999</v>
       </c>
       <c r="F5">
-        <v>20.415</v>
+        <v>27.22</v>
       </c>
       <c r="G5">
         <v>189.5</v>
@@ -1685,28 +1685,28 @@
         <v>132.6</v>
       </c>
       <c r="M5">
-        <v>1.0268745</v>
+        <v>1.369166</v>
       </c>
       <c r="N5">
-        <v>131.5731255</v>
+        <v>131.230834</v>
       </c>
       <c r="O5">
-        <v>38.81407202250001</v>
+        <v>38.71309603</v>
       </c>
       <c r="P5">
-        <v>92.75905347750003</v>
+        <v>92.51773797000001</v>
       </c>
       <c r="Q5">
-        <v>119.3590534775</v>
+        <v>119.11773797</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09710538924261067</v>
+        <v>0.09748552741771072</v>
       </c>
       <c r="T5">
-        <v>0.7936780545141355</v>
+        <v>0.7995586711845064</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>129.1297037758753</v>
+        <v>96.84727783190645</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09500456632100228</v>
+        <v>0.09475306007667222</v>
       </c>
       <c r="C6">
-        <v>628.761013374051</v>
+        <v>623.0171403683524</v>
       </c>
       <c r="D6">
-        <v>466.481013374051</v>
+        <v>467.5421403683524</v>
       </c>
       <c r="E6">
-        <v>-484.1799999999999</v>
+        <v>-477.375</v>
       </c>
       <c r="F6">
-        <v>27.22</v>
+        <v>34.025</v>
       </c>
       <c r="G6">
         <v>189.5</v>
@@ -1767,28 +1767,28 @@
         <v>132.6</v>
       </c>
       <c r="M6">
-        <v>1.369166</v>
+        <v>1.7114575</v>
       </c>
       <c r="N6">
-        <v>131.230834</v>
+        <v>130.8885425</v>
       </c>
       <c r="O6">
-        <v>38.71309603</v>
+        <v>38.61212003750001</v>
       </c>
       <c r="P6">
-        <v>92.51773797000001</v>
+        <v>92.27642246250002</v>
       </c>
       <c r="Q6">
-        <v>119.11773797</v>
+        <v>118.8764224625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09748552741771072</v>
+        <v>0.09787366850176024</v>
       </c>
       <c r="T6">
-        <v>0.7995586711845064</v>
+        <v>0.8055630903110957</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>96.84727783190645</v>
+        <v>77.47782226552516</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09475306007667222</v>
+        <v>0.09450155383234217</v>
       </c>
       <c r="C7">
-        <v>623.0171403683524</v>
+        <v>617.2781059633711</v>
       </c>
       <c r="D7">
-        <v>467.5421403683524</v>
+        <v>468.6081059633711</v>
       </c>
       <c r="E7">
-        <v>-477.375</v>
+        <v>-470.57</v>
       </c>
       <c r="F7">
-        <v>34.025</v>
+        <v>40.83000000000001</v>
       </c>
       <c r="G7">
         <v>189.5</v>
@@ -1849,28 +1849,28 @@
         <v>132.6</v>
       </c>
       <c r="M7">
-        <v>1.7114575</v>
+        <v>2.053749</v>
       </c>
       <c r="N7">
-        <v>130.8885425</v>
+        <v>130.546251</v>
       </c>
       <c r="O7">
-        <v>38.61212003750001</v>
+        <v>38.511144045</v>
       </c>
       <c r="P7">
-        <v>92.27642246250002</v>
+        <v>92.035106955</v>
       </c>
       <c r="Q7">
-        <v>118.8764224625</v>
+        <v>118.635106955</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09787366850176024</v>
+        <v>0.098270067906747</v>
       </c>
       <c r="T7">
-        <v>0.8055630903110957</v>
+        <v>0.811695263036123</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>77.47782226552516</v>
+        <v>64.56485188793762</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09450155383234217</v>
+        <v>0.09425004758801214</v>
       </c>
       <c r="C8">
-        <v>617.2781059633711</v>
+        <v>611.5439433298163</v>
       </c>
       <c r="D8">
-        <v>468.6081059633711</v>
+        <v>469.6789433298164</v>
       </c>
       <c r="E8">
-        <v>-470.57</v>
+        <v>-463.765</v>
       </c>
       <c r="F8">
-        <v>40.83</v>
+        <v>47.635</v>
       </c>
       <c r="G8">
         <v>189.5</v>
@@ -1931,28 +1931,28 @@
         <v>132.6</v>
       </c>
       <c r="M8">
-        <v>2.053749</v>
+        <v>2.3960405</v>
       </c>
       <c r="N8">
-        <v>130.546251</v>
+        <v>130.2039595</v>
       </c>
       <c r="O8">
-        <v>38.511144045</v>
+        <v>38.4101680525</v>
       </c>
       <c r="P8">
-        <v>92.035106955</v>
+        <v>91.79379144750001</v>
       </c>
       <c r="Q8">
-        <v>118.635106955</v>
+        <v>118.3937914475</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.098270067906747</v>
+        <v>0.09867499203012058</v>
       </c>
       <c r="T8">
-        <v>0.811695263036123</v>
+        <v>0.8179593104434091</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>64.56485188793764</v>
+        <v>55.34130161823226</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09425004758801213</v>
+        <v>0.09399854134368209</v>
       </c>
       <c r="C9">
-        <v>611.5439433298164</v>
+        <v>605.814685942292</v>
       </c>
       <c r="D9">
-        <v>469.6789433298164</v>
+        <v>470.754685942292</v>
       </c>
       <c r="E9">
-        <v>-463.765</v>
+        <v>-456.96</v>
       </c>
       <c r="F9">
-        <v>47.63500000000001</v>
+        <v>54.44</v>
       </c>
       <c r="G9">
         <v>189.5</v>
@@ -2013,28 +2013,28 @@
         <v>132.6</v>
       </c>
       <c r="M9">
-        <v>2.3960405</v>
+        <v>2.738332</v>
       </c>
       <c r="N9">
-        <v>130.2039595</v>
+        <v>129.861668</v>
       </c>
       <c r="O9">
-        <v>38.4101680525</v>
+        <v>38.30919206</v>
       </c>
       <c r="P9">
-        <v>91.79379144750001</v>
+        <v>91.55247594000001</v>
       </c>
       <c r="Q9">
-        <v>118.3937914475</v>
+        <v>118.15247594</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09867499203012058</v>
+        <v>0.09908871885182835</v>
       </c>
       <c r="T9">
-        <v>0.8179593104434091</v>
+        <v>0.8243595327943317</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>55.34130161823225</v>
+        <v>48.42363891595322</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09399854134368209</v>
+        <v>0.09374703509935203</v>
       </c>
       <c r="C10">
-        <v>605.814685942292</v>
+        <v>600.0903675827833</v>
       </c>
       <c r="D10">
-        <v>470.754685942292</v>
+        <v>471.8353675827833</v>
       </c>
       <c r="E10">
-        <v>-456.96</v>
+        <v>-450.155</v>
       </c>
       <c r="F10">
-        <v>54.44</v>
+        <v>61.245</v>
       </c>
       <c r="G10">
         <v>189.5</v>
@@ -2095,28 +2095,28 @@
         <v>132.6</v>
       </c>
       <c r="M10">
-        <v>2.738332</v>
+        <v>3.0806235</v>
       </c>
       <c r="N10">
-        <v>129.861668</v>
+        <v>129.5193765</v>
       </c>
       <c r="O10">
-        <v>38.30919206</v>
+        <v>38.2082160675</v>
       </c>
       <c r="P10">
-        <v>91.55247594000001</v>
+        <v>91.31116043250002</v>
       </c>
       <c r="Q10">
-        <v>118.15247594</v>
+        <v>117.9111604325</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09908871885182835</v>
+        <v>0.09951153857071653</v>
       </c>
       <c r="T10">
-        <v>0.8243595327943317</v>
+        <v>0.8309004193727474</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>48.42363891595322</v>
+        <v>43.04323459195842</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09374703509935203</v>
+        <v>0.09349552885502199</v>
       </c>
       <c r="C11">
-        <v>600.0903675827833</v>
+        <v>594.3710223441942</v>
       </c>
       <c r="D11">
-        <v>471.8353675827833</v>
+        <v>472.9210223441942</v>
       </c>
       <c r="E11">
-        <v>-450.155</v>
+        <v>-443.35</v>
       </c>
       <c r="F11">
-        <v>61.245</v>
+        <v>68.05</v>
       </c>
       <c r="G11">
         <v>189.5</v>
@@ -2177,28 +2177,28 @@
         <v>132.6</v>
       </c>
       <c r="M11">
-        <v>3.0806235</v>
+        <v>3.422915</v>
       </c>
       <c r="N11">
-        <v>129.5193765</v>
+        <v>129.177085</v>
       </c>
       <c r="O11">
-        <v>38.2082160675</v>
+        <v>38.10724007500001</v>
       </c>
       <c r="P11">
-        <v>91.31116043250002</v>
+        <v>91.06984492500003</v>
       </c>
       <c r="Q11">
-        <v>117.9111604325</v>
+        <v>117.669844925</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09951153857071653</v>
+        <v>0.09994375428335776</v>
       </c>
       <c r="T11">
-        <v>0.8309004193727474</v>
+        <v>0.8375866589862387</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>43.04323459195842</v>
+        <v>38.73891113276259</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09349552885502199</v>
+        <v>0.09324402261069194</v>
       </c>
       <c r="C12">
-        <v>594.3710223441942</v>
+        <v>588.6566846339322</v>
       </c>
       <c r="D12">
-        <v>472.9210223441942</v>
+        <v>474.0116846339322</v>
       </c>
       <c r="E12">
-        <v>-443.35</v>
+        <v>-436.545</v>
       </c>
       <c r="F12">
-        <v>68.05</v>
+        <v>74.855</v>
       </c>
       <c r="G12">
         <v>189.5</v>
@@ -2259,28 +2259,28 @@
         <v>132.6</v>
       </c>
       <c r="M12">
-        <v>3.422915</v>
+        <v>3.7652065</v>
       </c>
       <c r="N12">
-        <v>129.177085</v>
+        <v>128.8347935</v>
       </c>
       <c r="O12">
-        <v>38.10724007500001</v>
+        <v>38.0062640825</v>
       </c>
       <c r="P12">
-        <v>91.06984492500003</v>
+        <v>90.82852941750002</v>
       </c>
       <c r="Q12">
-        <v>117.669844925</v>
+        <v>117.4285294175</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09994375428335776</v>
+        <v>0.1003856827086426</v>
       </c>
       <c r="T12">
-        <v>0.8375866589862387</v>
+        <v>0.8444231511753141</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>38.73891113276259</v>
+        <v>35.21719193887507</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09324402261069194</v>
+        <v>0.09299251636636188</v>
       </c>
       <c r="C13">
-        <v>588.6566846339322</v>
+        <v>582.9473891775436</v>
       </c>
       <c r="D13">
-        <v>474.0116846339322</v>
+        <v>475.1073891775436</v>
       </c>
       <c r="E13">
-        <v>-436.545</v>
+        <v>-429.74</v>
       </c>
       <c r="F13">
-        <v>74.855</v>
+        <v>81.66</v>
       </c>
       <c r="G13">
         <v>189.5</v>
@@ -2341,28 +2341,28 @@
         <v>132.6</v>
       </c>
       <c r="M13">
-        <v>3.7652065</v>
+        <v>4.107498</v>
       </c>
       <c r="N13">
-        <v>128.8347935</v>
+        <v>128.492502</v>
       </c>
       <c r="O13">
-        <v>38.0062640825</v>
+        <v>37.90528809000001</v>
       </c>
       <c r="P13">
-        <v>90.82852941750002</v>
+        <v>90.58721391000003</v>
       </c>
       <c r="Q13">
-        <v>117.4285294175</v>
+        <v>117.18721391</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1003856827086426</v>
+        <v>0.1008376549617749</v>
       </c>
       <c r="T13">
-        <v>0.8444231511753141</v>
+        <v>0.8514150181868686</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.21719193887507</v>
+        <v>32.28242594396882</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09299251636636188</v>
+        <v>0.09274101012203184</v>
       </c>
       <c r="C14">
-        <v>582.9473891775436</v>
+        <v>577.2431710223983</v>
       </c>
       <c r="D14">
-        <v>475.1073891775436</v>
+        <v>476.2081710223983</v>
       </c>
       <c r="E14">
-        <v>-429.74</v>
+        <v>-422.9349999999999</v>
       </c>
       <c r="F14">
-        <v>81.66</v>
+        <v>88.465</v>
       </c>
       <c r="G14">
         <v>189.5</v>
@@ -2423,28 +2423,28 @@
         <v>132.6</v>
       </c>
       <c r="M14">
-        <v>4.107498</v>
+        <v>4.4497895</v>
       </c>
       <c r="N14">
-        <v>128.492502</v>
+        <v>128.1502105</v>
       </c>
       <c r="O14">
-        <v>37.90528809000001</v>
+        <v>37.8043120975</v>
       </c>
       <c r="P14">
-        <v>90.58721391000003</v>
+        <v>90.34589840250001</v>
       </c>
       <c r="Q14">
-        <v>117.18721391</v>
+        <v>116.9458984025</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1008376549617749</v>
+        <v>0.1013000173816458</v>
       </c>
       <c r="T14">
-        <v>0.8514150181868686</v>
+        <v>0.8585676177734014</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.28242594396882</v>
+        <v>29.79916240981737</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09274101012203184</v>
+        <v>0.09248950387770177</v>
       </c>
       <c r="C15">
-        <v>577.2431710223983</v>
+        <v>571.5440655414279</v>
       </c>
       <c r="D15">
-        <v>476.2081710223983</v>
+        <v>477.3140655414279</v>
       </c>
       <c r="E15">
-        <v>-422.9349999999999</v>
+        <v>-416.13</v>
       </c>
       <c r="F15">
-        <v>88.465</v>
+        <v>95.27000000000001</v>
       </c>
       <c r="G15">
         <v>189.5</v>
@@ -2505,28 +2505,28 @@
         <v>132.6</v>
       </c>
       <c r="M15">
-        <v>4.4497895</v>
+        <v>4.792081</v>
       </c>
       <c r="N15">
-        <v>128.1502105</v>
+        <v>127.807919</v>
       </c>
       <c r="O15">
-        <v>37.8043120975</v>
+        <v>37.70333610500001</v>
       </c>
       <c r="P15">
-        <v>90.34589840250001</v>
+        <v>90.10458289500002</v>
       </c>
       <c r="Q15">
-        <v>116.9458984025</v>
+        <v>116.704582895</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1013000173816458</v>
+        <v>0.1017731324159323</v>
       </c>
       <c r="T15">
-        <v>0.8585676177734014</v>
+        <v>0.8658865568852022</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.79916240981737</v>
+        <v>27.67065080911613</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09248950387770177</v>
+        <v>0.09223799763337172</v>
       </c>
       <c r="C16">
-        <v>571.5440655414279</v>
+        <v>565.8501084369132</v>
       </c>
       <c r="D16">
-        <v>477.3140655414279</v>
+        <v>478.4251084369132</v>
       </c>
       <c r="E16">
-        <v>-416.13</v>
+        <v>-409.3249999999999</v>
       </c>
       <c r="F16">
-        <v>95.27000000000001</v>
+        <v>102.075</v>
       </c>
       <c r="G16">
         <v>189.5</v>
@@ -2587,28 +2587,28 @@
         <v>132.6</v>
       </c>
       <c r="M16">
-        <v>4.792081</v>
+        <v>5.1343725</v>
       </c>
       <c r="N16">
-        <v>127.807919</v>
+        <v>127.4656275</v>
       </c>
       <c r="O16">
-        <v>37.70333610500001</v>
+        <v>37.60236011250001</v>
       </c>
       <c r="P16">
-        <v>90.10458289500002</v>
+        <v>89.86326738750002</v>
       </c>
       <c r="Q16">
-        <v>116.704582895</v>
+        <v>116.4632673875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1017731324159323</v>
+        <v>0.1022573795686726</v>
       </c>
       <c r="T16">
-        <v>0.8658865568852022</v>
+        <v>0.8733777063290455</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.67065080911613</v>
+        <v>25.82594075517505</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09223799763337172</v>
+        <v>0.09198649138904168</v>
       </c>
       <c r="C17">
-        <v>565.8501084369132</v>
+        <v>560.1613357443274</v>
       </c>
       <c r="D17">
-        <v>478.4251084369132</v>
+        <v>479.5413357443273</v>
       </c>
       <c r="E17">
-        <v>-409.325</v>
+        <v>-402.52</v>
       </c>
       <c r="F17">
-        <v>102.075</v>
+        <v>108.88</v>
       </c>
       <c r="G17">
         <v>189.5</v>
@@ -2669,28 +2669,28 @@
         <v>132.6</v>
       </c>
       <c r="M17">
-        <v>5.1343725</v>
+        <v>5.476664</v>
       </c>
       <c r="N17">
-        <v>127.4656275</v>
+        <v>127.123336</v>
       </c>
       <c r="O17">
-        <v>37.60236011250001</v>
+        <v>37.50138412</v>
       </c>
       <c r="P17">
-        <v>89.86326738750002</v>
+        <v>89.62195188000001</v>
       </c>
       <c r="Q17">
-        <v>116.4632673875</v>
+        <v>116.22195188</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1022573795686726</v>
+        <v>0.1027531564155258</v>
       </c>
       <c r="T17">
-        <v>0.8733777063290455</v>
+        <v>0.8810472164739327</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.82594075517505</v>
+        <v>24.21181945797661</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09198649138904168</v>
+        <v>0.09173498514471162</v>
       </c>
       <c r="C18">
-        <v>560.1613357443274</v>
+        <v>554.4777838362318</v>
       </c>
       <c r="D18">
-        <v>479.5413357443273</v>
+        <v>480.6627838362318</v>
       </c>
       <c r="E18">
-        <v>-402.52</v>
+        <v>-395.715</v>
       </c>
       <c r="F18">
-        <v>108.88</v>
+        <v>115.685</v>
       </c>
       <c r="G18">
         <v>189.5</v>
@@ -2751,28 +2751,28 @@
         <v>132.6</v>
       </c>
       <c r="M18">
-        <v>5.476664</v>
+        <v>5.8189555</v>
       </c>
       <c r="N18">
-        <v>127.123336</v>
+        <v>126.7810445</v>
       </c>
       <c r="O18">
-        <v>37.50138412</v>
+        <v>37.40040812750001</v>
       </c>
       <c r="P18">
-        <v>89.62195188000001</v>
+        <v>89.38063637250002</v>
       </c>
       <c r="Q18">
-        <v>116.22195188</v>
+        <v>115.9806363725</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1027531564155258</v>
+        <v>0.1032608796924236</v>
       </c>
       <c r="T18">
-        <v>0.8810472164739327</v>
+        <v>0.8889015340921906</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.21181945797661</v>
+        <v>22.78759478397799</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09173498514471162</v>
+        <v>0.09148347890038157</v>
       </c>
       <c r="C19">
-        <v>554.4777838362318</v>
+        <v>548.7994894262265</v>
       </c>
       <c r="D19">
-        <v>480.6627838362318</v>
+        <v>481.7894894262265</v>
       </c>
       <c r="E19">
-        <v>-395.715</v>
+        <v>-388.91</v>
       </c>
       <c r="F19">
-        <v>115.685</v>
+        <v>122.49</v>
       </c>
       <c r="G19">
         <v>189.5</v>
@@ -2833,28 +2833,28 @@
         <v>132.6</v>
       </c>
       <c r="M19">
-        <v>5.8189555</v>
+        <v>6.161247</v>
       </c>
       <c r="N19">
-        <v>126.7810445</v>
+        <v>126.438753</v>
       </c>
       <c r="O19">
-        <v>37.40040812750001</v>
+        <v>37.299432135</v>
       </c>
       <c r="P19">
-        <v>89.38063637250002</v>
+        <v>89.13932086500002</v>
       </c>
       <c r="Q19">
-        <v>115.9806363725</v>
+        <v>115.739320865</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1032608796924236</v>
+        <v>0.10378098646388</v>
       </c>
       <c r="T19">
-        <v>0.8889015340921906</v>
+        <v>0.8969474204328451</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.78759478397799</v>
+        <v>21.52161729597921</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09148347890038158</v>
+        <v>0.09123197265605151</v>
       </c>
       <c r="C20">
-        <v>548.7994894262264</v>
+        <v>543.1264895729568</v>
       </c>
       <c r="D20">
-        <v>481.7894894262264</v>
+        <v>482.9214895729568</v>
       </c>
       <c r="E20">
-        <v>-388.91</v>
+        <v>-382.105</v>
       </c>
       <c r="F20">
-        <v>122.49</v>
+        <v>129.295</v>
       </c>
       <c r="G20">
         <v>189.5</v>
@@ -2915,28 +2915,28 @@
         <v>132.6</v>
       </c>
       <c r="M20">
-        <v>6.161246999999999</v>
+        <v>6.503538499999999</v>
       </c>
       <c r="N20">
-        <v>126.438753</v>
+        <v>126.0964615</v>
       </c>
       <c r="O20">
-        <v>37.299432135</v>
+        <v>37.19845614250001</v>
       </c>
       <c r="P20">
-        <v>89.13932086500002</v>
+        <v>88.89800535750001</v>
       </c>
       <c r="Q20">
-        <v>115.739320865</v>
+        <v>115.4980053575</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.10378098646388</v>
+        <v>0.1043139353778414</v>
       </c>
       <c r="T20">
-        <v>0.8969474204328451</v>
+        <v>0.9051919706337627</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.52161729597921</v>
+        <v>20.38890059619083</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09123197265605151</v>
+        <v>0.09098046641172147</v>
       </c>
       <c r="C21">
-        <v>543.1264895729568</v>
+        <v>537.4588216841764</v>
       </c>
       <c r="D21">
-        <v>482.9214895729568</v>
+        <v>484.0588216841765</v>
       </c>
       <c r="E21">
-        <v>-382.105</v>
+        <v>-375.3</v>
       </c>
       <c r="F21">
-        <v>129.295</v>
+        <v>136.1</v>
       </c>
       <c r="G21">
         <v>189.5</v>
@@ -2997,28 +2997,28 @@
         <v>132.6</v>
       </c>
       <c r="M21">
-        <v>6.503538499999999</v>
+        <v>6.845829999999999</v>
       </c>
       <c r="N21">
-        <v>126.0964615</v>
+        <v>125.75417</v>
       </c>
       <c r="O21">
-        <v>37.19845614250001</v>
+        <v>37.09748015</v>
       </c>
       <c r="P21">
-        <v>88.89800535750001</v>
+        <v>88.65668985000002</v>
       </c>
       <c r="Q21">
-        <v>115.4980053575</v>
+        <v>115.25668985</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1043139353778414</v>
+        <v>0.1048602080146518</v>
       </c>
       <c r="T21">
-        <v>0.9051919706337627</v>
+        <v>0.9136426345897032</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.38890059619083</v>
+        <v>19.36945556638129</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09098046641172147</v>
+        <v>0.09072896016739143</v>
       </c>
       <c r="C22">
-        <v>537.4588216841764</v>
+        <v>531.7965235208683</v>
       </c>
       <c r="D22">
-        <v>484.0588216841765</v>
+        <v>485.2015235208682</v>
       </c>
       <c r="E22">
-        <v>-375.3</v>
+        <v>-368.495</v>
       </c>
       <c r="F22">
-        <v>136.1</v>
+        <v>142.905</v>
       </c>
       <c r="G22">
         <v>189.5</v>
@@ -3079,28 +3079,28 @@
         <v>132.6</v>
       </c>
       <c r="M22">
-        <v>6.845829999999999</v>
+        <v>7.188121499999999</v>
       </c>
       <c r="N22">
-        <v>125.75417</v>
+        <v>125.4118785</v>
       </c>
       <c r="O22">
-        <v>37.09748015</v>
+        <v>36.99650415750001</v>
       </c>
       <c r="P22">
-        <v>88.65668985000002</v>
+        <v>88.41537434250003</v>
       </c>
       <c r="Q22">
-        <v>115.25668985</v>
+        <v>115.0153743425</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1048602080146518</v>
+        <v>0.1054203103384702</v>
       </c>
       <c r="T22">
-        <v>0.9136426345897032</v>
+        <v>0.9223072394052878</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.36945556638129</v>
+        <v>18.44710053941076</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09072896016739143</v>
+        <v>0.09047745392306138</v>
       </c>
       <c r="C23">
-        <v>531.7965235208683</v>
+        <v>526.1396332014233</v>
       </c>
       <c r="D23">
-        <v>485.2015235208682</v>
+        <v>486.3496332014234</v>
       </c>
       <c r="E23">
-        <v>-368.495</v>
+        <v>-361.6899999999999</v>
       </c>
       <c r="F23">
-        <v>142.905</v>
+        <v>149.71</v>
       </c>
       <c r="G23">
         <v>189.5</v>
@@ -3161,28 +3161,28 @@
         <v>132.6</v>
       </c>
       <c r="M23">
-        <v>7.188121499999999</v>
+        <v>7.530413</v>
       </c>
       <c r="N23">
-        <v>125.4118785</v>
+        <v>125.069587</v>
       </c>
       <c r="O23">
-        <v>36.99650415750001</v>
+        <v>36.89552816500001</v>
       </c>
       <c r="P23">
-        <v>88.41537434250003</v>
+        <v>88.17405883500001</v>
       </c>
       <c r="Q23">
-        <v>115.0153743425</v>
+        <v>114.774058835</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1054203103384702</v>
+        <v>0.1059947742603351</v>
       </c>
       <c r="T23">
-        <v>0.9223072394052878</v>
+        <v>0.9311940135751181</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.44710053941076</v>
+        <v>17.60859596943754</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09047745392306138</v>
+        <v>0.09022594767873132</v>
       </c>
       <c r="C24">
-        <v>526.1396332014233</v>
+        <v>520.4881892058794</v>
       </c>
       <c r="D24">
-        <v>486.3496332014234</v>
+        <v>487.5031892058794</v>
       </c>
       <c r="E24">
-        <v>-361.6899999999999</v>
+        <v>-354.885</v>
       </c>
       <c r="F24">
-        <v>149.71</v>
+        <v>156.515</v>
       </c>
       <c r="G24">
         <v>189.5</v>
@@ -3243,28 +3243,28 @@
         <v>132.6</v>
       </c>
       <c r="M24">
-        <v>7.530413</v>
+        <v>7.8727045</v>
       </c>
       <c r="N24">
-        <v>125.069587</v>
+        <v>124.7272955</v>
       </c>
       <c r="O24">
-        <v>36.89552816500001</v>
+        <v>36.7945521725</v>
       </c>
       <c r="P24">
-        <v>88.17405883500001</v>
+        <v>87.93274332750002</v>
       </c>
       <c r="Q24">
-        <v>114.774058835</v>
+        <v>114.5327433275</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1059947742603351</v>
+        <v>0.1065841593230277</v>
       </c>
       <c r="T24">
-        <v>0.9311940135751181</v>
+        <v>0.9403116130480609</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.60859596943754</v>
+        <v>16.84300484033156</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09022594767873132</v>
+        <v>0.08997444143440127</v>
       </c>
       <c r="C25">
-        <v>520.4881892058794</v>
+        <v>514.8422303802203</v>
       </c>
       <c r="D25">
-        <v>487.5031892058794</v>
+        <v>488.6622303802203</v>
       </c>
       <c r="E25">
-        <v>-354.885</v>
+        <v>-348.0799999999999</v>
       </c>
       <c r="F25">
-        <v>156.515</v>
+        <v>163.32</v>
       </c>
       <c r="G25">
         <v>189.5</v>
@@ -3325,28 +3325,28 @@
         <v>132.6</v>
       </c>
       <c r="M25">
-        <v>7.8727045</v>
+        <v>8.214996000000001</v>
       </c>
       <c r="N25">
-        <v>124.7272955</v>
+        <v>124.385004</v>
       </c>
       <c r="O25">
-        <v>36.7945521725</v>
+        <v>36.69357618000001</v>
       </c>
       <c r="P25">
-        <v>87.93274332750002</v>
+        <v>87.69142782000002</v>
       </c>
       <c r="Q25">
-        <v>114.5327433275</v>
+        <v>114.29142782</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1065841593230277</v>
+        <v>0.107189054518949</v>
       </c>
       <c r="T25">
-        <v>0.9403116130480609</v>
+        <v>0.9496691493492391</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.84300484033156</v>
+        <v>16.14121297198441</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08997444143440125</v>
+        <v>0.0897229351900712</v>
       </c>
       <c r="C26">
-        <v>514.8422303802204</v>
+        <v>509.2017959407361</v>
       </c>
       <c r="D26">
-        <v>488.6622303802204</v>
+        <v>489.8267959407361</v>
       </c>
       <c r="E26">
-        <v>-348.08</v>
+        <v>-341.275</v>
       </c>
       <c r="F26">
-        <v>163.32</v>
+        <v>170.125</v>
       </c>
       <c r="G26">
         <v>189.5</v>
@@ -3407,28 +3407,28 @@
         <v>132.6</v>
       </c>
       <c r="M26">
-        <v>8.214995999999999</v>
+        <v>8.557287499999999</v>
       </c>
       <c r="N26">
-        <v>124.385004</v>
+        <v>124.0427125</v>
       </c>
       <c r="O26">
-        <v>36.69357618000001</v>
+        <v>36.5926001875</v>
       </c>
       <c r="P26">
-        <v>87.69142782000002</v>
+        <v>87.45011231250001</v>
       </c>
       <c r="Q26">
-        <v>114.29142782</v>
+        <v>114.0501123125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.107189054518949</v>
+        <v>0.1078100802534283</v>
       </c>
       <c r="T26">
-        <v>0.9496691493492391</v>
+        <v>0.9592762199517819</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.14121297198441</v>
+        <v>15.49556445310503</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0897229351900712</v>
+        <v>0.08947142894574116</v>
       </c>
       <c r="C27">
-        <v>509.2017959407361</v>
+        <v>503.5669254784464</v>
       </c>
       <c r="D27">
-        <v>489.8267959407361</v>
+        <v>490.9969254784464</v>
       </c>
       <c r="E27">
-        <v>-341.275</v>
+        <v>-334.47</v>
       </c>
       <c r="F27">
-        <v>170.125</v>
+        <v>176.93</v>
       </c>
       <c r="G27">
         <v>189.5</v>
@@ -3489,28 +3489,28 @@
         <v>132.6</v>
       </c>
       <c r="M27">
-        <v>8.557287499999999</v>
+        <v>8.899578999999999</v>
       </c>
       <c r="N27">
-        <v>124.0427125</v>
+        <v>123.700421</v>
       </c>
       <c r="O27">
-        <v>36.5926001875</v>
+        <v>36.49162419500001</v>
       </c>
       <c r="P27">
-        <v>87.45011231250001</v>
+        <v>87.20879680500002</v>
       </c>
       <c r="Q27">
-        <v>114.0501123125</v>
+        <v>113.808796805</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1078100802534283</v>
+        <v>0.1084478904672178</v>
       </c>
       <c r="T27">
-        <v>0.9592762199517819</v>
+        <v>0.9691429411111503</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.49556445310503</v>
+        <v>14.89958120490869</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08947142894574116</v>
+        <v>0.0892199227014111</v>
       </c>
       <c r="C28">
-        <v>503.5669254784464</v>
+        <v>497.9376589635872</v>
       </c>
       <c r="D28">
-        <v>490.9969254784464</v>
+        <v>492.1726589635872</v>
       </c>
       <c r="E28">
-        <v>-334.47</v>
+        <v>-327.665</v>
       </c>
       <c r="F28">
-        <v>176.93</v>
+        <v>183.735</v>
       </c>
       <c r="G28">
         <v>189.5</v>
@@ -3571,28 +3571,28 @@
         <v>132.6</v>
       </c>
       <c r="M28">
-        <v>8.899578999999999</v>
+        <v>9.241870500000001</v>
       </c>
       <c r="N28">
-        <v>123.700421</v>
+        <v>123.3581295</v>
       </c>
       <c r="O28">
-        <v>36.49162419500001</v>
+        <v>36.3906482025</v>
       </c>
       <c r="P28">
-        <v>87.20879680500002</v>
+        <v>86.96748129750002</v>
       </c>
       <c r="Q28">
-        <v>113.808796805</v>
+        <v>113.5674812975</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1084478904672178</v>
+        <v>0.1091031749334399</v>
       </c>
       <c r="T28">
-        <v>0.9691429411111503</v>
+        <v>0.9792799833981726</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.89958120490869</v>
+        <v>14.34774486398614</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0892199227014111</v>
+        <v>0.08896841645708106</v>
       </c>
       <c r="C29">
-        <v>497.9376589635872</v>
+        <v>492.3140367501614</v>
       </c>
       <c r="D29">
-        <v>492.1726589635872</v>
+        <v>493.3540367501615</v>
       </c>
       <c r="E29">
-        <v>-327.665</v>
+        <v>-320.86</v>
       </c>
       <c r="F29">
-        <v>183.735</v>
+        <v>190.54</v>
       </c>
       <c r="G29">
         <v>189.5</v>
@@ -3653,28 +3653,28 @@
         <v>132.6</v>
       </c>
       <c r="M29">
-        <v>9.241870500000001</v>
+        <v>9.584162000000001</v>
       </c>
       <c r="N29">
-        <v>123.3581295</v>
+        <v>123.015838</v>
       </c>
       <c r="O29">
-        <v>36.3906482025</v>
+        <v>36.28967221000001</v>
       </c>
       <c r="P29">
-        <v>86.96748129750002</v>
+        <v>86.72616579000001</v>
       </c>
       <c r="Q29">
-        <v>113.5674812975</v>
+        <v>113.32616579</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1091031749334399</v>
+        <v>0.1097766617459459</v>
       </c>
       <c r="T29">
-        <v>0.9792799833981726</v>
+        <v>0.9896986101931676</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.34774486398614</v>
+        <v>13.83532540455806</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08896841645708106</v>
+        <v>0.08871691021275101</v>
       </c>
       <c r="C30">
-        <v>492.3140367501614</v>
+        <v>486.6960995805568</v>
       </c>
       <c r="D30">
-        <v>493.3540367501615</v>
+        <v>494.5410995805569</v>
       </c>
       <c r="E30">
-        <v>-320.86</v>
+        <v>-314.0549999999999</v>
       </c>
       <c r="F30">
-        <v>190.54</v>
+        <v>197.345</v>
       </c>
       <c r="G30">
         <v>189.5</v>
@@ -3735,28 +3735,28 @@
         <v>132.6</v>
       </c>
       <c r="M30">
-        <v>9.584162000000001</v>
+        <v>9.926453500000001</v>
       </c>
       <c r="N30">
-        <v>123.015838</v>
+        <v>122.6735465</v>
       </c>
       <c r="O30">
-        <v>36.28967221000001</v>
+        <v>36.1886962175</v>
       </c>
       <c r="P30">
-        <v>86.72616579000001</v>
+        <v>86.48485028250002</v>
       </c>
       <c r="Q30">
-        <v>113.32616579</v>
+        <v>113.0848502825</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1097766617459459</v>
+        <v>0.1104691200179592</v>
       </c>
       <c r="T30">
-        <v>0.9896986101931676</v>
+        <v>1.000410719433092</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.83532540455806</v>
+        <v>13.35824521819399</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08871691021275101</v>
+        <v>0.08846540396842095</v>
       </c>
       <c r="C31">
-        <v>486.6960995805568</v>
+        <v>481.0838885902286</v>
       </c>
       <c r="D31">
-        <v>494.5410995805569</v>
+        <v>495.7338885902286</v>
       </c>
       <c r="E31">
-        <v>-314.0549999999999</v>
+        <v>-307.25</v>
       </c>
       <c r="F31">
-        <v>197.345</v>
+        <v>204.15</v>
       </c>
       <c r="G31">
         <v>189.5</v>
@@ -3817,28 +3817,28 @@
         <v>132.6</v>
       </c>
       <c r="M31">
-        <v>9.926453499999999</v>
+        <v>10.268745</v>
       </c>
       <c r="N31">
-        <v>122.6735465</v>
+        <v>122.331255</v>
       </c>
       <c r="O31">
-        <v>36.18869621750001</v>
+        <v>36.08772022500001</v>
       </c>
       <c r="P31">
-        <v>86.48485028250002</v>
+        <v>86.24353477500003</v>
       </c>
       <c r="Q31">
-        <v>113.0848502825</v>
+        <v>112.843534775</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1104691200179592</v>
+        <v>0.1111813628120299</v>
       </c>
       <c r="T31">
-        <v>1.000410719433092</v>
+        <v>1.011428888937015</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.35824521819399</v>
+        <v>12.91297037758753</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08846540396842095</v>
+        <v>0.0885417227240909</v>
       </c>
       <c r="C32">
-        <v>481.0838885902286</v>
+        <v>473.9163329898817</v>
       </c>
       <c r="D32">
-        <v>495.7338885902286</v>
+        <v>495.3713329898818</v>
       </c>
       <c r="E32">
-        <v>-307.25</v>
+        <v>-300.4449999999999</v>
       </c>
       <c r="F32">
-        <v>204.15</v>
+        <v>210.955</v>
       </c>
       <c r="G32">
         <v>189.5</v>
@@ -3899,45 +3899,45 @@
         <v>132.6</v>
       </c>
       <c r="M32">
-        <v>10.268745</v>
+        <v>10.927469</v>
       </c>
       <c r="N32">
-        <v>122.331255</v>
+        <v>121.672531</v>
       </c>
       <c r="O32">
-        <v>36.08772022500001</v>
+        <v>35.893396645</v>
       </c>
       <c r="P32">
-        <v>86.24353477500003</v>
+        <v>85.77913435500002</v>
       </c>
       <c r="Q32">
-        <v>112.843534775</v>
+        <v>112.379134355</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1111813628120299</v>
+        <v>0.1119142503247694</v>
       </c>
       <c r="T32">
-        <v>1.011428888937015</v>
+        <v>1.022766425672935</v>
       </c>
       <c r="U32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V32">
         <v>0.295</v>
       </c>
       <c r="W32">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>12.91297037758753</v>
+        <v>12.1345574167266</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0885417227240909</v>
+        <v>0.08830079147976083</v>
       </c>
       <c r="C33">
-        <v>473.9163329898817</v>
+        <v>468.2576971100848</v>
       </c>
       <c r="D33">
-        <v>495.3713329898818</v>
+        <v>496.5176971100848</v>
       </c>
       <c r="E33">
-        <v>-300.4449999999999</v>
+        <v>-293.64</v>
       </c>
       <c r="F33">
-        <v>210.955</v>
+        <v>217.76</v>
       </c>
       <c r="G33">
         <v>189.5</v>
@@ -3981,28 +3981,28 @@
         <v>132.6</v>
       </c>
       <c r="M33">
-        <v>10.927469</v>
+        <v>11.279968</v>
       </c>
       <c r="N33">
-        <v>121.672531</v>
+        <v>121.320032</v>
       </c>
       <c r="O33">
-        <v>35.893396645</v>
+        <v>35.78940944000001</v>
       </c>
       <c r="P33">
-        <v>85.77913435500002</v>
+        <v>85.53062256000001</v>
       </c>
       <c r="Q33">
-        <v>112.379134355</v>
+        <v>112.13062256</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1119142503247694</v>
+        <v>0.1126686933525895</v>
       </c>
       <c r="T33">
-        <v>1.022766425672935</v>
+        <v>1.034437419371676</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.1345574167266</v>
+        <v>11.7553524974539</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08830079147976083</v>
+        <v>0.08805986023543079</v>
       </c>
       <c r="C34">
-        <v>468.2576971100848</v>
+        <v>462.6043792566073</v>
       </c>
       <c r="D34">
-        <v>496.5176971100848</v>
+        <v>497.6693792566072</v>
       </c>
       <c r="E34">
-        <v>-293.64</v>
+        <v>-286.835</v>
       </c>
       <c r="F34">
-        <v>217.76</v>
+        <v>224.565</v>
       </c>
       <c r="G34">
         <v>189.5</v>
@@ -4063,28 +4063,28 @@
         <v>132.6</v>
       </c>
       <c r="M34">
-        <v>11.279968</v>
+        <v>11.632467</v>
       </c>
       <c r="N34">
-        <v>121.320032</v>
+        <v>120.967533</v>
       </c>
       <c r="O34">
-        <v>35.78940944000001</v>
+        <v>35.685422235</v>
       </c>
       <c r="P34">
-        <v>85.53062256000001</v>
+        <v>85.28211076500001</v>
       </c>
       <c r="Q34">
-        <v>112.13062256</v>
+        <v>111.882110765</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1126686933525895</v>
+        <v>0.1134456570678072</v>
       </c>
       <c r="T34">
-        <v>1.034437419371676</v>
+        <v>1.046456800942022</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.7553524974539</v>
+        <v>11.39912969450075</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08805986023543079</v>
+        <v>0.08781892899110073</v>
       </c>
       <c r="C35">
-        <v>462.6043792566073</v>
+        <v>456.9564165212709</v>
       </c>
       <c r="D35">
-        <v>497.6693792566072</v>
+        <v>498.8264165212709</v>
       </c>
       <c r="E35">
-        <v>-286.835</v>
+        <v>-280.03</v>
       </c>
       <c r="F35">
-        <v>224.565</v>
+        <v>231.37</v>
       </c>
       <c r="G35">
         <v>189.5</v>
@@ -4145,28 +4145,28 @@
         <v>132.6</v>
       </c>
       <c r="M35">
-        <v>11.632467</v>
+        <v>11.984966</v>
       </c>
       <c r="N35">
-        <v>120.967533</v>
+        <v>120.615034</v>
       </c>
       <c r="O35">
-        <v>35.685422235</v>
+        <v>35.58143503</v>
       </c>
       <c r="P35">
-        <v>85.28211076500001</v>
+        <v>85.03359897000001</v>
       </c>
       <c r="Q35">
-        <v>111.882110765</v>
+        <v>111.63359897</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1134456570678072</v>
+        <v>0.1142461651380314</v>
       </c>
       <c r="T35">
-        <v>1.046456800942022</v>
+        <v>1.058840406196317</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.39912969450075</v>
+        <v>11.06386117407425</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08781892899110073</v>
+        <v>0.08757799774677071</v>
       </c>
       <c r="C36">
-        <v>456.9564165212709</v>
+        <v>451.3138463416419</v>
       </c>
       <c r="D36">
-        <v>498.8264165212709</v>
+        <v>499.9888463416418</v>
       </c>
       <c r="E36">
-        <v>-280.03</v>
+        <v>-273.225</v>
       </c>
       <c r="F36">
-        <v>231.37</v>
+        <v>238.175</v>
       </c>
       <c r="G36">
         <v>189.5</v>
@@ -4227,28 +4227,28 @@
         <v>132.6</v>
       </c>
       <c r="M36">
-        <v>11.984966</v>
+        <v>12.337465</v>
       </c>
       <c r="N36">
-        <v>120.615034</v>
+        <v>120.262535</v>
       </c>
       <c r="O36">
-        <v>35.58143503</v>
+        <v>35.47744782500001</v>
       </c>
       <c r="P36">
-        <v>85.03359897000001</v>
+        <v>84.78508717500003</v>
       </c>
       <c r="Q36">
-        <v>111.63359897</v>
+        <v>111.385087175</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1142461651380314</v>
+        <v>0.1150713042258011</v>
       </c>
       <c r="T36">
-        <v>1.058840406196317</v>
+        <v>1.071605045458437</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.06386117407425</v>
+        <v>10.74775085481499</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08757799774677071</v>
+        <v>0.08733706650244065</v>
       </c>
       <c r="C37">
-        <v>451.3138463416419</v>
+        <v>445.6767065050692</v>
       </c>
       <c r="D37">
-        <v>499.9888463416418</v>
+        <v>501.1567065050692</v>
       </c>
       <c r="E37">
-        <v>-273.225</v>
+        <v>-266.42</v>
       </c>
       <c r="F37">
-        <v>238.175</v>
+        <v>244.98</v>
       </c>
       <c r="G37">
         <v>189.5</v>
@@ -4309,28 +4309,28 @@
         <v>132.6</v>
       </c>
       <c r="M37">
-        <v>12.337465</v>
+        <v>12.689964</v>
       </c>
       <c r="N37">
-        <v>120.262535</v>
+        <v>119.910036</v>
       </c>
       <c r="O37">
-        <v>35.47744782500001</v>
+        <v>35.37346062</v>
       </c>
       <c r="P37">
-        <v>84.78508717500003</v>
+        <v>84.53657538000002</v>
       </c>
       <c r="Q37">
-        <v>111.385087175</v>
+        <v>111.13657538</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1150713042258011</v>
+        <v>0.1159222289100635</v>
       </c>
       <c r="T37">
-        <v>1.071605045458437</v>
+        <v>1.084768579697498</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.74775085481499</v>
+        <v>10.44920221995902</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08733706650244066</v>
+        <v>0.08709613525811058</v>
       </c>
       <c r="C38">
-        <v>445.6767065050692</v>
+        <v>440.0450351527792</v>
       </c>
       <c r="D38">
-        <v>501.1567065050692</v>
+        <v>502.3300351527792</v>
       </c>
       <c r="E38">
-        <v>-266.42</v>
+        <v>-259.615</v>
       </c>
       <c r="F38">
-        <v>244.98</v>
+        <v>251.785</v>
       </c>
       <c r="G38">
         <v>189.5</v>
@@ -4391,28 +4391,28 @@
         <v>132.6</v>
       </c>
       <c r="M38">
-        <v>12.689964</v>
+        <v>13.042463</v>
       </c>
       <c r="N38">
-        <v>119.910036</v>
+        <v>119.557537</v>
       </c>
       <c r="O38">
-        <v>35.37346062</v>
+        <v>35.26947341500001</v>
       </c>
       <c r="P38">
-        <v>84.53657538000002</v>
+        <v>84.28806358500002</v>
       </c>
       <c r="Q38">
-        <v>111.13657538</v>
+        <v>110.888063585</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1159222289100635</v>
+        <v>0.116800167076366</v>
       </c>
       <c r="T38">
-        <v>1.084768579697498</v>
+        <v>1.098350003912403</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.44920221995902</v>
+        <v>10.16679134914932</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08709613525811058</v>
+        <v>0.08685520401378054</v>
       </c>
       <c r="C39">
-        <v>440.0450351527792</v>
+        <v>434.4188707840269</v>
       </c>
       <c r="D39">
-        <v>502.3300351527792</v>
+        <v>503.5088707840268</v>
       </c>
       <c r="E39">
-        <v>-259.615</v>
+        <v>-252.81</v>
       </c>
       <c r="F39">
-        <v>251.785</v>
+        <v>258.59</v>
       </c>
       <c r="G39">
         <v>189.5</v>
@@ -4473,28 +4473,28 @@
         <v>132.6</v>
       </c>
       <c r="M39">
-        <v>13.042463</v>
+        <v>13.394962</v>
       </c>
       <c r="N39">
-        <v>119.557537</v>
+        <v>119.205038</v>
       </c>
       <c r="O39">
-        <v>35.26947341500001</v>
+        <v>35.16548621</v>
       </c>
       <c r="P39">
-        <v>84.28806358500002</v>
+        <v>84.03955179000002</v>
       </c>
       <c r="Q39">
-        <v>110.888063585</v>
+        <v>110.63955179</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.116800167076366</v>
+        <v>0.1177064258286783</v>
       </c>
       <c r="T39">
-        <v>1.098350003912403</v>
+        <v>1.112369538585852</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.16679134914932</v>
+        <v>9.89924420838223</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08685520401378054</v>
+        <v>0.08708168776945049</v>
       </c>
       <c r="C40">
-        <v>434.4188707840269</v>
+        <v>426.5055686615542</v>
       </c>
       <c r="D40">
-        <v>503.5088707840268</v>
+        <v>502.4005686615542</v>
       </c>
       <c r="E40">
-        <v>-252.81</v>
+        <v>-246.005</v>
       </c>
       <c r="F40">
-        <v>258.59</v>
+        <v>265.395</v>
       </c>
       <c r="G40">
         <v>189.5</v>
@@ -4555,45 +4555,45 @@
         <v>132.6</v>
       </c>
       <c r="M40">
-        <v>13.394962</v>
+        <v>14.1986325</v>
       </c>
       <c r="N40">
-        <v>119.205038</v>
+        <v>118.4013675</v>
       </c>
       <c r="O40">
-        <v>35.16548621</v>
+        <v>34.9284034125</v>
       </c>
       <c r="P40">
-        <v>84.03955179000002</v>
+        <v>83.47296408750002</v>
       </c>
       <c r="Q40">
-        <v>110.63955179</v>
+        <v>110.0729640875</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1177064258286783</v>
+        <v>0.1186423979827057</v>
       </c>
       <c r="T40">
-        <v>1.112369538585852</v>
+        <v>1.126848730133841</v>
       </c>
       <c r="U40">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V40">
         <v>0.295</v>
       </c>
       <c r="W40">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>9.89924420838223</v>
+        <v>9.338927534042453</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08708168776945049</v>
+        <v>0.08685274152512044</v>
       </c>
       <c r="C41">
-        <v>426.5055686615542</v>
+        <v>420.8209478869343</v>
       </c>
       <c r="D41">
-        <v>502.4005686615542</v>
+        <v>503.5209478869343</v>
       </c>
       <c r="E41">
-        <v>-246.005</v>
+        <v>-239.2</v>
       </c>
       <c r="F41">
-        <v>265.395</v>
+        <v>272.2</v>
       </c>
       <c r="G41">
         <v>189.5</v>
@@ -4637,28 +4637,28 @@
         <v>132.6</v>
       </c>
       <c r="M41">
-        <v>14.1986325</v>
+        <v>14.5627</v>
       </c>
       <c r="N41">
-        <v>118.4013675</v>
+        <v>118.0373</v>
       </c>
       <c r="O41">
-        <v>34.9284034125</v>
+        <v>34.8210035</v>
       </c>
       <c r="P41">
-        <v>83.47296408750002</v>
+        <v>83.21629650000001</v>
       </c>
       <c r="Q41">
-        <v>110.0729640875</v>
+        <v>109.8162965</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1186423979827057</v>
+        <v>0.1196095692085341</v>
       </c>
       <c r="T41">
-        <v>1.126848730133841</v>
+        <v>1.141810561400097</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.338927534042453</v>
+        <v>9.105454345691392</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08685274152512044</v>
+        <v>0.08662379528079039</v>
       </c>
       <c r="C42">
-        <v>420.8209478869343</v>
+        <v>415.1413352879221</v>
       </c>
       <c r="D42">
-        <v>503.5209478869343</v>
+        <v>504.6463352879221</v>
       </c>
       <c r="E42">
-        <v>-239.2</v>
+        <v>-232.395</v>
       </c>
       <c r="F42">
-        <v>272.2</v>
+        <v>279.005</v>
       </c>
       <c r="G42">
         <v>189.5</v>
@@ -4719,28 +4719,28 @@
         <v>132.6</v>
       </c>
       <c r="M42">
-        <v>14.5627</v>
+        <v>14.9267675</v>
       </c>
       <c r="N42">
-        <v>118.0373</v>
+        <v>117.6732325</v>
       </c>
       <c r="O42">
-        <v>34.8210035</v>
+        <v>34.7136035875</v>
       </c>
       <c r="P42">
-        <v>83.21629650000001</v>
+        <v>82.95962891250002</v>
       </c>
       <c r="Q42">
-        <v>109.8162965</v>
+        <v>109.5596289125</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1196095692085341</v>
+        <v>0.1206095258996447</v>
       </c>
       <c r="T42">
-        <v>1.141810561400097</v>
+        <v>1.157279573387242</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.105454345691392</v>
+        <v>8.883370093357456</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08662379528079039</v>
+        <v>0.08639484903646033</v>
       </c>
       <c r="C43">
-        <v>415.1413352879221</v>
+        <v>409.4667645200959</v>
       </c>
       <c r="D43">
-        <v>504.6463352879221</v>
+        <v>505.7767645200959</v>
       </c>
       <c r="E43">
-        <v>-232.395</v>
+        <v>-225.59</v>
       </c>
       <c r="F43">
-        <v>279.005</v>
+        <v>285.81</v>
       </c>
       <c r="G43">
         <v>189.5</v>
@@ -4801,28 +4801,28 @@
         <v>132.6</v>
       </c>
       <c r="M43">
-        <v>14.9267675</v>
+        <v>15.290835</v>
       </c>
       <c r="N43">
-        <v>117.6732325</v>
+        <v>117.309165</v>
       </c>
       <c r="O43">
-        <v>34.7136035875</v>
+        <v>34.606203675</v>
       </c>
       <c r="P43">
-        <v>82.95962891250002</v>
+        <v>82.70296132500002</v>
       </c>
       <c r="Q43">
-        <v>109.5596289125</v>
+        <v>109.302961325</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1206095258996447</v>
+        <v>0.1216439638559661</v>
       </c>
       <c r="T43">
-        <v>1.157279573387242</v>
+        <v>1.173281999580841</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.883370093357456</v>
+        <v>8.671861281610848</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08639484903646034</v>
+        <v>0.08616590279213029</v>
       </c>
       <c r="C44">
-        <v>409.4667645200958</v>
+        <v>403.7972695412708</v>
       </c>
       <c r="D44">
-        <v>505.7767645200958</v>
+        <v>506.9122695412708</v>
       </c>
       <c r="E44">
-        <v>-225.59</v>
+        <v>-218.785</v>
       </c>
       <c r="F44">
-        <v>285.81</v>
+        <v>292.615</v>
       </c>
       <c r="G44">
         <v>189.5</v>
@@ -4883,28 +4883,28 @@
         <v>132.6</v>
       </c>
       <c r="M44">
-        <v>15.290835</v>
+        <v>15.6549025</v>
       </c>
       <c r="N44">
-        <v>117.309165</v>
+        <v>116.9450975</v>
       </c>
       <c r="O44">
-        <v>34.606203675</v>
+        <v>34.4988037625</v>
       </c>
       <c r="P44">
-        <v>82.70296132500002</v>
+        <v>82.44629373750001</v>
       </c>
       <c r="Q44">
-        <v>109.302961325</v>
+        <v>109.0462937375</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1216439638559661</v>
+        <v>0.1227146978809303</v>
       </c>
       <c r="T44">
-        <v>1.173281999580841</v>
+        <v>1.189845914412811</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.671861281610848</v>
+        <v>8.470190089015247</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08616590279213029</v>
+        <v>0.08593695654780024</v>
       </c>
       <c r="C45">
-        <v>403.7972695412708</v>
+        <v>398.1328846148993</v>
       </c>
       <c r="D45">
-        <v>506.9122695412708</v>
+        <v>508.0528846148993</v>
       </c>
       <c r="E45">
-        <v>-218.785</v>
+        <v>-211.98</v>
       </c>
       <c r="F45">
-        <v>292.615</v>
+        <v>299.42</v>
       </c>
       <c r="G45">
         <v>189.5</v>
@@ -4965,28 +4965,28 @@
         <v>132.6</v>
       </c>
       <c r="M45">
-        <v>15.6549025</v>
+        <v>16.01897</v>
       </c>
       <c r="N45">
-        <v>116.9450975</v>
+        <v>116.58103</v>
       </c>
       <c r="O45">
-        <v>34.4988037625</v>
+        <v>34.39140385</v>
       </c>
       <c r="P45">
-        <v>82.44629373750001</v>
+        <v>82.18962615000002</v>
       </c>
       <c r="Q45">
-        <v>109.0462937375</v>
+        <v>108.78962615</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1227146978809303</v>
+        <v>0.1238236724067861</v>
       </c>
       <c r="T45">
-        <v>1.189845914412811</v>
+        <v>1.207001397631638</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.470190089015247</v>
+        <v>8.277685768810356</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08593695654780024</v>
+        <v>0.08570801030347018</v>
       </c>
       <c r="C46">
-        <v>398.1328846148993</v>
+        <v>392.473644313517</v>
       </c>
       <c r="D46">
-        <v>508.0528846148993</v>
+        <v>509.1986443135169</v>
       </c>
       <c r="E46">
-        <v>-211.98</v>
+        <v>-205.175</v>
       </c>
       <c r="F46">
-        <v>299.42</v>
+        <v>306.225</v>
       </c>
       <c r="G46">
         <v>189.5</v>
@@ -5047,28 +5047,28 @@
         <v>132.6</v>
       </c>
       <c r="M46">
-        <v>16.01897</v>
+        <v>16.3830375</v>
       </c>
       <c r="N46">
-        <v>116.58103</v>
+        <v>116.2169625</v>
       </c>
       <c r="O46">
-        <v>34.39140385</v>
+        <v>34.2840039375</v>
       </c>
       <c r="P46">
-        <v>82.18962615000002</v>
+        <v>81.93295856250002</v>
       </c>
       <c r="Q46">
-        <v>108.78962615</v>
+        <v>108.5329585625</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1238236724067861</v>
+        <v>0.1249729732790367</v>
       </c>
       <c r="T46">
-        <v>1.207001397631638</v>
+        <v>1.224780716603876</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.277685768810356</v>
+        <v>8.093737196170125</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08570801030347018</v>
+        <v>0.08547906405914016</v>
       </c>
       <c r="C47">
-        <v>392.473644313517</v>
+        <v>386.8195835222357</v>
       </c>
       <c r="D47">
-        <v>509.1986443135169</v>
+        <v>510.3495835222358</v>
       </c>
       <c r="E47">
-        <v>-205.175</v>
+        <v>-198.3699999999999</v>
       </c>
       <c r="F47">
-        <v>306.225</v>
+        <v>313.03</v>
       </c>
       <c r="G47">
         <v>189.5</v>
@@ -5129,28 +5129,28 @@
         <v>132.6</v>
       </c>
       <c r="M47">
-        <v>16.3830375</v>
+        <v>16.747105</v>
       </c>
       <c r="N47">
-        <v>116.2169625</v>
+        <v>115.852895</v>
       </c>
       <c r="O47">
-        <v>34.2840039375</v>
+        <v>34.176604025</v>
       </c>
       <c r="P47">
-        <v>81.93295856250002</v>
+        <v>81.67629097500001</v>
       </c>
       <c r="Q47">
-        <v>108.5329585625</v>
+        <v>108.276290975</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1249729732790367</v>
+        <v>0.1261648408502595</v>
       </c>
       <c r="T47">
-        <v>1.224780716603876</v>
+        <v>1.243218528871383</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.093737196170125</v>
+        <v>7.91778638755773</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08547906405914016</v>
+        <v>0.08525011781481009</v>
       </c>
       <c r="C48">
-        <v>386.8195835222357</v>
+        <v>381.1707374422855</v>
       </c>
       <c r="D48">
-        <v>510.3495835222358</v>
+        <v>511.5057374422855</v>
       </c>
       <c r="E48">
-        <v>-198.3699999999999</v>
+        <v>-191.5649999999999</v>
       </c>
       <c r="F48">
-        <v>313.03</v>
+        <v>319.835</v>
       </c>
       <c r="G48">
         <v>189.5</v>
@@ -5211,28 +5211,28 @@
         <v>132.6</v>
       </c>
       <c r="M48">
-        <v>16.747105</v>
+        <v>17.1111725</v>
       </c>
       <c r="N48">
-        <v>115.852895</v>
+        <v>115.4888275</v>
       </c>
       <c r="O48">
-        <v>34.176604025</v>
+        <v>34.0692041125</v>
       </c>
       <c r="P48">
-        <v>81.67629097500001</v>
+        <v>81.41962338750001</v>
       </c>
       <c r="Q48">
-        <v>108.276290975</v>
+        <v>108.0196233875</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1261648408502595</v>
+        <v>0.1274016845562455</v>
       </c>
       <c r="T48">
-        <v>1.243218528871383</v>
+        <v>1.26235210763955</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.91778638755773</v>
+        <v>7.749322847396927</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08525011781481009</v>
+        <v>0.08529189157048003</v>
       </c>
       <c r="C49">
-        <v>381.1707374422855</v>
+        <v>374.1543939298782</v>
       </c>
       <c r="D49">
-        <v>511.5057374422855</v>
+        <v>511.2943939298782</v>
       </c>
       <c r="E49">
-        <v>-191.5649999999999</v>
+        <v>-184.7599999999999</v>
       </c>
       <c r="F49">
-        <v>319.835</v>
+        <v>326.64</v>
       </c>
       <c r="G49">
         <v>189.5</v>
@@ -5293,45 +5293,45 @@
         <v>132.6</v>
       </c>
       <c r="M49">
-        <v>17.1111725</v>
+        <v>17.736552</v>
       </c>
       <c r="N49">
-        <v>115.4888275</v>
+        <v>114.863448</v>
       </c>
       <c r="O49">
-        <v>34.0692041125</v>
+        <v>33.88471716</v>
       </c>
       <c r="P49">
-        <v>81.41962338750001</v>
+        <v>80.97873084000003</v>
       </c>
       <c r="Q49">
-        <v>108.0196233875</v>
+        <v>107.57873084</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1274016845562455</v>
+        <v>0.1286860991740001</v>
       </c>
       <c r="T49">
-        <v>1.26235210763955</v>
+        <v>1.282221593283416</v>
       </c>
       <c r="U49">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V49">
         <v>0.295</v>
       </c>
       <c r="W49">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y49">
-        <v>7.749322847396927</v>
+        <v>7.476086671186147</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08529189157048003</v>
+        <v>0.08506858532614998</v>
       </c>
       <c r="C50">
-        <v>374.1543939298782</v>
+        <v>368.4811871095398</v>
       </c>
       <c r="D50">
-        <v>511.2943939298782</v>
+        <v>512.4261871095398</v>
       </c>
       <c r="E50">
-        <v>-184.76</v>
+        <v>-177.955</v>
       </c>
       <c r="F50">
-        <v>326.64</v>
+        <v>333.445</v>
       </c>
       <c r="G50">
         <v>189.5</v>
@@ -5375,28 +5375,28 @@
         <v>132.6</v>
       </c>
       <c r="M50">
-        <v>17.736552</v>
+        <v>18.1060635</v>
       </c>
       <c r="N50">
-        <v>114.863448</v>
+        <v>114.4939365</v>
       </c>
       <c r="O50">
-        <v>33.88471716</v>
+        <v>33.7757112675</v>
       </c>
       <c r="P50">
-        <v>80.97873084000003</v>
+        <v>80.71822523250002</v>
       </c>
       <c r="Q50">
-        <v>107.57873084</v>
+        <v>107.3182252325</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1286860991740001</v>
+        <v>0.1300208829924509</v>
       </c>
       <c r="T50">
-        <v>1.282221593283416</v>
+        <v>1.302870274442727</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.476086671186148</v>
+        <v>7.323513473815002</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08506858532614998</v>
+        <v>0.08484527908181994</v>
       </c>
       <c r="C51">
-        <v>368.4811871095398</v>
+        <v>362.8130020442247</v>
       </c>
       <c r="D51">
-        <v>512.4261871095398</v>
+        <v>513.5630020442247</v>
       </c>
       <c r="E51">
-        <v>-177.955</v>
+        <v>-171.15</v>
       </c>
       <c r="F51">
-        <v>333.445</v>
+        <v>340.25</v>
       </c>
       <c r="G51">
         <v>189.5</v>
@@ -5457,28 +5457,28 @@
         <v>132.6</v>
       </c>
       <c r="M51">
-        <v>18.1060635</v>
+        <v>18.475575</v>
       </c>
       <c r="N51">
-        <v>114.4939365</v>
+        <v>114.124425</v>
       </c>
       <c r="O51">
-        <v>33.7757112675</v>
+        <v>33.66670537500001</v>
       </c>
       <c r="P51">
-        <v>80.71822523250002</v>
+        <v>80.45771962500002</v>
       </c>
       <c r="Q51">
-        <v>107.3182252325</v>
+        <v>107.057719625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1300208829924509</v>
+        <v>0.1314090581636399</v>
       </c>
       <c r="T51">
-        <v>1.302870274442727</v>
+        <v>1.324344902848412</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.323513473815002</v>
+        <v>7.177043204338704</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08484527908181994</v>
+        <v>0.08462197283748989</v>
       </c>
       <c r="C52">
-        <v>362.8130020442247</v>
+        <v>357.1498722304602</v>
       </c>
       <c r="D52">
-        <v>513.5630020442247</v>
+        <v>514.7048722304602</v>
       </c>
       <c r="E52">
-        <v>-171.15</v>
+        <v>-164.345</v>
       </c>
       <c r="F52">
-        <v>340.25</v>
+        <v>347.055</v>
       </c>
       <c r="G52">
         <v>189.5</v>
@@ -5539,28 +5539,28 @@
         <v>132.6</v>
       </c>
       <c r="M52">
-        <v>18.475575</v>
+        <v>18.8450865</v>
       </c>
       <c r="N52">
-        <v>114.124425</v>
+        <v>113.7549135</v>
       </c>
       <c r="O52">
-        <v>33.66670537500001</v>
+        <v>33.55769948250001</v>
       </c>
       <c r="P52">
-        <v>80.45771962500002</v>
+        <v>80.19721401750002</v>
       </c>
       <c r="Q52">
-        <v>107.057719625</v>
+        <v>106.7972140175</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1314090581636399</v>
+        <v>0.1328538935458977</v>
       </c>
       <c r="T52">
-        <v>1.324344902848412</v>
+        <v>1.346696046699225</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.177043204338704</v>
+        <v>7.036316866998727</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08462197283748989</v>
+        <v>0.08439866659315982</v>
       </c>
       <c r="C53">
-        <v>357.1498722304602</v>
+        <v>351.4918314633455</v>
       </c>
       <c r="D53">
-        <v>514.7048722304602</v>
+        <v>515.8518314633455</v>
       </c>
       <c r="E53">
-        <v>-164.345</v>
+        <v>-157.54</v>
       </c>
       <c r="F53">
-        <v>347.055</v>
+        <v>353.86</v>
       </c>
       <c r="G53">
         <v>189.5</v>
@@ -5621,28 +5621,28 @@
         <v>132.6</v>
       </c>
       <c r="M53">
-        <v>18.8450865</v>
+        <v>19.214598</v>
       </c>
       <c r="N53">
-        <v>113.7549135</v>
+        <v>113.385402</v>
       </c>
       <c r="O53">
-        <v>33.55769948250001</v>
+        <v>33.44869359</v>
       </c>
       <c r="P53">
-        <v>80.19721401750002</v>
+        <v>79.93670841000002</v>
       </c>
       <c r="Q53">
-        <v>106.7972140175</v>
+        <v>106.53670841</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1328538935458977</v>
+        <v>0.1343589304024163</v>
       </c>
       <c r="T53">
-        <v>1.346696046699225</v>
+        <v>1.36997848821049</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.036316866998727</v>
+        <v>6.901003081094906</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08439866659315982</v>
+        <v>0.08417536034882978</v>
       </c>
       <c r="C54">
-        <v>351.4918314633455</v>
+        <v>345.8389138398866</v>
       </c>
       <c r="D54">
-        <v>515.8518314633455</v>
+        <v>517.0039138398866</v>
       </c>
       <c r="E54">
-        <v>-157.54</v>
+        <v>-150.735</v>
       </c>
       <c r="F54">
-        <v>353.86</v>
+        <v>360.665</v>
       </c>
       <c r="G54">
         <v>189.5</v>
@@ -5703,28 +5703,28 @@
         <v>132.6</v>
       </c>
       <c r="M54">
-        <v>19.214598</v>
+        <v>19.5841095</v>
       </c>
       <c r="N54">
-        <v>113.385402</v>
+        <v>113.0158905</v>
       </c>
       <c r="O54">
-        <v>33.44869359</v>
+        <v>33.3396876975</v>
       </c>
       <c r="P54">
-        <v>79.93670841000002</v>
+        <v>79.67620280250003</v>
       </c>
       <c r="Q54">
-        <v>106.53670841</v>
+        <v>106.2762028025</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1343589304024163</v>
+        <v>0.1359280113804889</v>
       </c>
       <c r="T54">
-        <v>1.36997848821049</v>
+        <v>1.394251671913724</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.901003081094906</v>
+        <v>6.770795475791229</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08417536034882978</v>
+        <v>0.08395205410449973</v>
       </c>
       <c r="C55">
-        <v>345.8389138398866</v>
+        <v>340.1911537623744</v>
       </c>
       <c r="D55">
-        <v>517.0039138398866</v>
+        <v>518.1611537623744</v>
       </c>
       <c r="E55">
-        <v>-150.735</v>
+        <v>-143.9299999999999</v>
       </c>
       <c r="F55">
-        <v>360.665</v>
+        <v>367.47</v>
       </c>
       <c r="G55">
         <v>189.5</v>
@@ -5785,28 +5785,28 @@
         <v>132.6</v>
       </c>
       <c r="M55">
-        <v>19.5841095</v>
+        <v>19.953621</v>
       </c>
       <c r="N55">
-        <v>113.0158905</v>
+        <v>112.646379</v>
       </c>
       <c r="O55">
-        <v>33.3396876975</v>
+        <v>33.230681805</v>
       </c>
       <c r="P55">
-        <v>79.67620280250003</v>
+        <v>79.41569719500002</v>
       </c>
       <c r="Q55">
-        <v>106.2762028025</v>
+        <v>106.015697195</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1359280113804889</v>
+        <v>0.1375653132706516</v>
       </c>
       <c r="T55">
-        <v>1.394251671913724</v>
+        <v>1.419580211430141</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.770795475791229</v>
+        <v>6.645410374387687</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08395205410449973</v>
+        <v>0.08372874786016968</v>
       </c>
       <c r="C56">
-        <v>340.1911537623744</v>
+        <v>334.5485859418094</v>
       </c>
       <c r="D56">
-        <v>518.1611537623744</v>
+        <v>519.3235859418095</v>
       </c>
       <c r="E56">
-        <v>-143.9299999999999</v>
+        <v>-137.1249999999999</v>
       </c>
       <c r="F56">
-        <v>367.47</v>
+        <v>374.275</v>
       </c>
       <c r="G56">
         <v>189.5</v>
@@ -5867,28 +5867,28 @@
         <v>132.6</v>
       </c>
       <c r="M56">
-        <v>19.953621</v>
+        <v>20.3231325</v>
       </c>
       <c r="N56">
-        <v>112.646379</v>
+        <v>112.2768675</v>
       </c>
       <c r="O56">
-        <v>33.230681805</v>
+        <v>33.1216759125</v>
       </c>
       <c r="P56">
-        <v>79.41569719500002</v>
+        <v>79.15519158750001</v>
       </c>
       <c r="Q56">
-        <v>106.015697195</v>
+        <v>105.7551915875</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1375653132706516</v>
+        <v>0.1392753841337104</v>
       </c>
       <c r="T56">
-        <v>1.419580211430141</v>
+        <v>1.446034463813955</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.645410374387687</v>
+        <v>6.524584731217002</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08372874786016968</v>
+        <v>0.08350544161583963</v>
       </c>
       <c r="C57">
-        <v>334.5485859418094</v>
+        <v>328.9112454013725</v>
       </c>
       <c r="D57">
-        <v>519.3235859418095</v>
+        <v>520.4912454013726</v>
       </c>
       <c r="E57">
-        <v>-137.1249999999999</v>
+        <v>-130.3199999999999</v>
       </c>
       <c r="F57">
-        <v>374.275</v>
+        <v>381.08</v>
       </c>
       <c r="G57">
         <v>189.5</v>
@@ -5949,28 +5949,28 @@
         <v>132.6</v>
       </c>
       <c r="M57">
-        <v>20.3231325</v>
+        <v>20.692644</v>
       </c>
       <c r="N57">
-        <v>112.2768675</v>
+        <v>111.907356</v>
       </c>
       <c r="O57">
-        <v>33.1216759125</v>
+        <v>33.01267002</v>
       </c>
       <c r="P57">
-        <v>79.15519158750001</v>
+        <v>78.89468598000002</v>
       </c>
       <c r="Q57">
-        <v>105.7551915875</v>
+        <v>105.49468598</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1392753841337104</v>
+        <v>0.1410631854905446</v>
       </c>
       <c r="T57">
-        <v>1.446034463813955</v>
+        <v>1.473691182215215</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.524584731217002</v>
+        <v>6.408074289588127</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08350544161583963</v>
+        <v>0.08328213537150958</v>
       </c>
       <c r="C58">
-        <v>328.9112454013725</v>
+        <v>323.279167479942</v>
       </c>
       <c r="D58">
-        <v>520.4912454013726</v>
+        <v>521.6641674799421</v>
       </c>
       <c r="E58">
-        <v>-130.3199999999999</v>
+        <v>-123.5149999999999</v>
       </c>
       <c r="F58">
-        <v>381.08</v>
+        <v>387.885</v>
       </c>
       <c r="G58">
         <v>189.5</v>
@@ -6031,28 +6031,28 @@
         <v>132.6</v>
       </c>
       <c r="M58">
-        <v>20.692644</v>
+        <v>21.0621555</v>
       </c>
       <c r="N58">
-        <v>111.907356</v>
+        <v>111.5378445</v>
       </c>
       <c r="O58">
-        <v>33.01267002</v>
+        <v>32.9036641275</v>
       </c>
       <c r="P58">
-        <v>78.89468598000002</v>
+        <v>78.63418037250003</v>
       </c>
       <c r="Q58">
-        <v>105.49468598</v>
+        <v>105.2341803725</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1410631854905446</v>
+        <v>0.1429341403988595</v>
       </c>
       <c r="T58">
-        <v>1.473691182215215</v>
+        <v>1.502634259611882</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.408074289588127</v>
+        <v>6.29565193363044</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08328213537150958</v>
+        <v>0.08305882912717952</v>
       </c>
       <c r="C59">
-        <v>323.279167479942</v>
+        <v>317.6523878356593</v>
       </c>
       <c r="D59">
-        <v>521.6641674799421</v>
+        <v>522.8423878356593</v>
       </c>
       <c r="E59">
-        <v>-123.5149999999999</v>
+        <v>-116.7099999999999</v>
       </c>
       <c r="F59">
-        <v>387.885</v>
+        <v>394.6900000000001</v>
       </c>
       <c r="G59">
         <v>189.5</v>
@@ -6113,28 +6113,28 @@
         <v>132.6</v>
       </c>
       <c r="M59">
-        <v>21.0621555</v>
+        <v>21.431667</v>
       </c>
       <c r="N59">
-        <v>111.5378445</v>
+        <v>111.168333</v>
       </c>
       <c r="O59">
-        <v>32.9036641275</v>
+        <v>32.79465823500001</v>
       </c>
       <c r="P59">
-        <v>78.63418037250003</v>
+        <v>78.373674765</v>
       </c>
       <c r="Q59">
-        <v>105.2341803725</v>
+        <v>104.973674765</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1429341403988595</v>
+        <v>0.1448941883980465</v>
       </c>
       <c r="T59">
-        <v>1.502634259611882</v>
+        <v>1.532955578789343</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.29565193363044</v>
+        <v>6.187106210636811</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08305882912717952</v>
+        <v>0.08325147288284948</v>
       </c>
       <c r="C60">
-        <v>317.6523878356593</v>
+        <v>309.8306359299647</v>
       </c>
       <c r="D60">
-        <v>522.8423878356593</v>
+        <v>521.8256359299647</v>
       </c>
       <c r="E60">
-        <v>-116.71</v>
+        <v>-109.905</v>
       </c>
       <c r="F60">
-        <v>394.69</v>
+        <v>401.495</v>
       </c>
       <c r="G60">
         <v>189.5</v>
@@ -6195,45 +6195,45 @@
         <v>132.6</v>
       </c>
       <c r="M60">
-        <v>21.431667</v>
+        <v>22.2026735</v>
       </c>
       <c r="N60">
-        <v>111.168333</v>
+        <v>110.3973265</v>
       </c>
       <c r="O60">
-        <v>32.79465823500001</v>
+        <v>32.5672113175</v>
       </c>
       <c r="P60">
-        <v>78.373674765</v>
+        <v>77.83011518250001</v>
       </c>
       <c r="Q60">
-        <v>104.973674765</v>
+        <v>104.4301151825</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1448941883980465</v>
+        <v>0.1469498484947548</v>
       </c>
       <c r="T60">
-        <v>1.532955578789343</v>
+        <v>1.564755986707168</v>
       </c>
       <c r="U60">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V60">
         <v>0.295</v>
       </c>
       <c r="W60">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>6.187106210636812</v>
+        <v>5.972253746829184</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08325147288284948</v>
+        <v>0.08303521663851943</v>
       </c>
       <c r="C61">
-        <v>309.8306359299647</v>
+        <v>304.1672845263692</v>
       </c>
       <c r="D61">
-        <v>521.8256359299647</v>
+        <v>522.9672845263692</v>
       </c>
       <c r="E61">
-        <v>-109.905</v>
+        <v>-103.1</v>
       </c>
       <c r="F61">
-        <v>401.495</v>
+        <v>408.3</v>
       </c>
       <c r="G61">
         <v>189.5</v>
@@ -6277,28 +6277,28 @@
         <v>132.6</v>
       </c>
       <c r="M61">
-        <v>22.2026735</v>
+        <v>22.57899</v>
       </c>
       <c r="N61">
-        <v>110.3973265</v>
+        <v>110.02101</v>
       </c>
       <c r="O61">
-        <v>32.5672113175</v>
+        <v>32.45619795</v>
       </c>
       <c r="P61">
-        <v>77.83011518250001</v>
+        <v>77.56481205000001</v>
       </c>
       <c r="Q61">
-        <v>104.4301151825</v>
+        <v>104.16481205</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1469498484947548</v>
+        <v>0.1491082915962985</v>
       </c>
       <c r="T61">
-        <v>1.564755986707168</v>
+        <v>1.598146415020884</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.972253746829184</v>
+        <v>5.87271618438203</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08303521663851943</v>
+        <v>0.08281896039418937</v>
       </c>
       <c r="C62">
-        <v>304.1672845263692</v>
+        <v>298.5089394665422</v>
       </c>
       <c r="D62">
-        <v>522.9672845263692</v>
+        <v>524.1139394665422</v>
       </c>
       <c r="E62">
-        <v>-103.1</v>
+        <v>-96.29499999999996</v>
       </c>
       <c r="F62">
-        <v>408.3</v>
+        <v>415.105</v>
       </c>
       <c r="G62">
         <v>189.5</v>
@@ -6359,28 +6359,28 @@
         <v>132.6</v>
       </c>
       <c r="M62">
-        <v>22.57899</v>
+        <v>22.9553065</v>
       </c>
       <c r="N62">
-        <v>110.02101</v>
+        <v>109.6446935</v>
       </c>
       <c r="O62">
-        <v>32.45619795</v>
+        <v>32.3451845825</v>
       </c>
       <c r="P62">
-        <v>77.56481205000001</v>
+        <v>77.29950891750002</v>
       </c>
       <c r="Q62">
-        <v>104.16481205</v>
+        <v>103.8995089175</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1491082915962985</v>
+        <v>0.151377424087665</v>
       </c>
       <c r="T62">
-        <v>1.598146415020884</v>
+        <v>1.633249172991713</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.87271618438203</v>
+        <v>5.776442148572488</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08281896039418937</v>
+        <v>0.08260270414985932</v>
       </c>
       <c r="C63">
-        <v>298.5089394665422</v>
+        <v>292.855633753484</v>
       </c>
       <c r="D63">
-        <v>524.1139394665422</v>
+        <v>525.2656337534841</v>
       </c>
       <c r="E63">
-        <v>-96.29499999999996</v>
+        <v>-89.48999999999995</v>
       </c>
       <c r="F63">
-        <v>415.105</v>
+        <v>421.91</v>
       </c>
       <c r="G63">
         <v>189.5</v>
@@ -6441,28 +6441,28 @@
         <v>132.6</v>
       </c>
       <c r="M63">
-        <v>22.9553065</v>
+        <v>23.331623</v>
       </c>
       <c r="N63">
-        <v>109.6446935</v>
+        <v>109.268377</v>
       </c>
       <c r="O63">
-        <v>32.3451845825</v>
+        <v>32.234171215</v>
       </c>
       <c r="P63">
-        <v>77.29950891750002</v>
+        <v>77.03420578500001</v>
       </c>
       <c r="Q63">
-        <v>103.8995089175</v>
+        <v>103.634205785</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.151377424087665</v>
+        <v>0.1537659846048929</v>
       </c>
       <c r="T63">
-        <v>1.633249172991713</v>
+        <v>1.670199444539955</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.776442148572488</v>
+        <v>5.683273726821319</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08260270414985932</v>
+        <v>0.08238644790552926</v>
       </c>
       <c r="C64">
-        <v>292.855633753484</v>
+        <v>287.2074006809187</v>
       </c>
       <c r="D64">
-        <v>525.2656337534841</v>
+        <v>526.4224006809187</v>
       </c>
       <c r="E64">
-        <v>-89.48999999999995</v>
+        <v>-82.685</v>
       </c>
       <c r="F64">
-        <v>421.91</v>
+        <v>428.715</v>
       </c>
       <c r="G64">
         <v>189.5</v>
@@ -6523,28 +6523,28 @@
         <v>132.6</v>
       </c>
       <c r="M64">
-        <v>23.331623</v>
+        <v>23.7079395</v>
       </c>
       <c r="N64">
-        <v>109.268377</v>
+        <v>108.8920605</v>
       </c>
       <c r="O64">
-        <v>32.234171215</v>
+        <v>32.1231578475</v>
       </c>
       <c r="P64">
-        <v>77.03420578500001</v>
+        <v>76.76890265250003</v>
       </c>
       <c r="Q64">
-        <v>103.634205785</v>
+        <v>103.3689026525</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1537659846048929</v>
+        <v>0.1562836565014304</v>
       </c>
       <c r="T64">
-        <v>1.670199444539955</v>
+        <v>1.709147028063777</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.683273726821319</v>
+        <v>5.593063032744792</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08238644790552926</v>
+        <v>0.08217019166119921</v>
       </c>
       <c r="C65">
-        <v>287.2074006809187</v>
+        <v>281.5642738365024</v>
       </c>
       <c r="D65">
-        <v>526.4224006809187</v>
+        <v>527.5842738365023</v>
       </c>
       <c r="E65">
-        <v>-82.685</v>
+        <v>-75.88</v>
       </c>
       <c r="F65">
-        <v>428.715</v>
+        <v>435.52</v>
       </c>
       <c r="G65">
         <v>189.5</v>
@@ -6605,28 +6605,28 @@
         <v>132.6</v>
       </c>
       <c r="M65">
-        <v>23.7079395</v>
+        <v>24.084256</v>
       </c>
       <c r="N65">
-        <v>108.8920605</v>
+        <v>108.515744</v>
       </c>
       <c r="O65">
-        <v>32.1231578475</v>
+        <v>32.01214448</v>
       </c>
       <c r="P65">
-        <v>76.76890265250003</v>
+        <v>76.50359952000002</v>
       </c>
       <c r="Q65">
-        <v>103.3689026525</v>
+        <v>103.10359952</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1562836565014304</v>
+        <v>0.1589411990588867</v>
       </c>
       <c r="T65">
-        <v>1.709147028063777</v>
+        <v>1.750258366227813</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.593063032744792</v>
+        <v>5.505671422858153</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08217019166119921</v>
+        <v>0.08195393541686917</v>
       </c>
       <c r="C66">
-        <v>281.5642738365024</v>
+        <v>275.9262871050732</v>
       </c>
       <c r="D66">
-        <v>527.5842738365023</v>
+        <v>528.7512871050732</v>
       </c>
       <c r="E66">
-        <v>-75.88</v>
+        <v>-69.07499999999999</v>
       </c>
       <c r="F66">
-        <v>435.52</v>
+        <v>442.325</v>
       </c>
       <c r="G66">
         <v>189.5</v>
@@ -6687,28 +6687,28 @@
         <v>132.6</v>
       </c>
       <c r="M66">
-        <v>24.084256</v>
+        <v>24.4605725</v>
       </c>
       <c r="N66">
-        <v>108.515744</v>
+        <v>108.1394275</v>
       </c>
       <c r="O66">
-        <v>32.01214448</v>
+        <v>31.90113111250001</v>
       </c>
       <c r="P66">
-        <v>76.50359952000002</v>
+        <v>76.23829638750001</v>
       </c>
       <c r="Q66">
-        <v>103.10359952</v>
+        <v>102.8382963875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1589411990588867</v>
+        <v>0.1617506011910547</v>
       </c>
       <c r="T66">
-        <v>1.750258366227813</v>
+        <v>1.793718923715507</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.505671422858153</v>
+        <v>5.420968785583413</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08195393541686917</v>
+        <v>0.08173767917253912</v>
       </c>
       <c r="C67">
-        <v>275.9262871050732</v>
+        <v>270.2934746719473</v>
       </c>
       <c r="D67">
-        <v>528.7512871050732</v>
+        <v>529.9234746719472</v>
       </c>
       <c r="E67">
-        <v>-69.07499999999999</v>
+        <v>-62.26999999999998</v>
       </c>
       <c r="F67">
-        <v>442.325</v>
+        <v>449.13</v>
       </c>
       <c r="G67">
         <v>189.5</v>
@@ -6769,28 +6769,28 @@
         <v>132.6</v>
       </c>
       <c r="M67">
-        <v>24.4605725</v>
+        <v>24.836889</v>
       </c>
       <c r="N67">
-        <v>108.1394275</v>
+        <v>107.763111</v>
       </c>
       <c r="O67">
-        <v>31.90113111250001</v>
+        <v>31.79011774500001</v>
       </c>
       <c r="P67">
-        <v>76.23829638750001</v>
+        <v>75.97299325500002</v>
       </c>
       <c r="Q67">
-        <v>102.8382963875</v>
+        <v>102.572993255</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1617506011910547</v>
+        <v>0.1647252622721739</v>
       </c>
       <c r="T67">
-        <v>1.793718923715507</v>
+        <v>1.83973598458483</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.420968785583413</v>
+        <v>5.338832894892755</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08173767917253912</v>
+        <v>0.08152142292820906</v>
       </c>
       <c r="C68">
-        <v>270.2934746719473</v>
+        <v>264.6658710262548</v>
       </c>
       <c r="D68">
-        <v>529.9234746719472</v>
+        <v>531.1008710262548</v>
       </c>
       <c r="E68">
-        <v>-62.26999999999998</v>
+        <v>-55.46499999999997</v>
       </c>
       <c r="F68">
-        <v>449.13</v>
+        <v>455.935</v>
       </c>
       <c r="G68">
         <v>189.5</v>
@@ -6851,28 +6851,28 @@
         <v>132.6</v>
       </c>
       <c r="M68">
-        <v>24.836889</v>
+        <v>25.2132055</v>
       </c>
       <c r="N68">
-        <v>107.763111</v>
+        <v>107.3867945</v>
       </c>
       <c r="O68">
-        <v>31.79011774500001</v>
+        <v>31.6791043775</v>
       </c>
       <c r="P68">
-        <v>75.97299325500002</v>
+        <v>75.70769012250003</v>
       </c>
       <c r="Q68">
-        <v>102.572993255</v>
+        <v>102.3076901225</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1647252622721739</v>
+        <v>0.1678802058430578</v>
       </c>
       <c r="T68">
-        <v>1.83973598458483</v>
+        <v>1.888541958234112</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.338832894892755</v>
+        <v>5.259148821834654</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08152142292820906</v>
+        <v>0.08130516668387901</v>
       </c>
       <c r="C69">
-        <v>264.6658710262548</v>
+        <v>259.0435109643239</v>
       </c>
       <c r="D69">
-        <v>531.1008710262548</v>
+        <v>532.2835109643239</v>
       </c>
       <c r="E69">
-        <v>-55.46499999999997</v>
+        <v>-48.65999999999997</v>
       </c>
       <c r="F69">
-        <v>455.935</v>
+        <v>462.74</v>
       </c>
       <c r="G69">
         <v>189.5</v>
@@ -6933,28 +6933,28 @@
         <v>132.6</v>
       </c>
       <c r="M69">
-        <v>25.2132055</v>
+        <v>25.589522</v>
       </c>
       <c r="N69">
-        <v>107.3867945</v>
+        <v>107.010478</v>
       </c>
       <c r="O69">
-        <v>31.6791043775</v>
+        <v>31.56809101</v>
       </c>
       <c r="P69">
-        <v>75.70769012250003</v>
+        <v>75.44238699000002</v>
       </c>
       <c r="Q69">
-        <v>102.3076901225</v>
+        <v>102.04238699</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1678802058430578</v>
+        <v>0.1712323333871219</v>
       </c>
       <c r="T69">
-        <v>1.888541958234112</v>
+        <v>1.940398305236474</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.259148821834654</v>
+        <v>5.181808397984144</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08130516668387901</v>
+        <v>0.08108891043954897</v>
       </c>
       <c r="C70">
-        <v>259.0435109643239</v>
+        <v>253.4264295931081</v>
       </c>
       <c r="D70">
-        <v>532.2835109643239</v>
+        <v>533.4714295931082</v>
       </c>
       <c r="E70">
-        <v>-48.65999999999997</v>
+        <v>-41.85499999999996</v>
       </c>
       <c r="F70">
-        <v>462.74</v>
+        <v>469.545</v>
       </c>
       <c r="G70">
         <v>189.5</v>
@@ -7015,28 +7015,28 @@
         <v>132.6</v>
       </c>
       <c r="M70">
-        <v>25.589522</v>
+        <v>25.9658385</v>
       </c>
       <c r="N70">
-        <v>107.010478</v>
+        <v>106.6341615</v>
       </c>
       <c r="O70">
-        <v>31.56809101</v>
+        <v>31.4570776425</v>
       </c>
       <c r="P70">
-        <v>75.44238699000002</v>
+        <v>75.17708385750001</v>
       </c>
       <c r="Q70">
-        <v>102.04238699</v>
+        <v>101.7770838575</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1712323333871219</v>
+        <v>0.1748007272243515</v>
       </c>
       <c r="T70">
-        <v>1.940398305236474</v>
+        <v>1.995600223013182</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.181808397984144</v>
+        <v>5.106709725549591</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08108891043954897</v>
+        <v>0.0808726541952189</v>
       </c>
       <c r="C71">
-        <v>253.4264295931081</v>
+        <v>247.8146623336606</v>
       </c>
       <c r="D71">
-        <v>533.4714295931082</v>
+        <v>534.6646623336607</v>
       </c>
       <c r="E71">
-        <v>-41.85499999999996</v>
+        <v>-35.04999999999995</v>
       </c>
       <c r="F71">
-        <v>469.545</v>
+        <v>476.35</v>
       </c>
       <c r="G71">
         <v>189.5</v>
@@ -7097,28 +7097,28 @@
         <v>132.6</v>
       </c>
       <c r="M71">
-        <v>25.9658385</v>
+        <v>26.342155</v>
       </c>
       <c r="N71">
-        <v>106.6341615</v>
+        <v>106.257845</v>
       </c>
       <c r="O71">
-        <v>31.4570776425</v>
+        <v>31.346064275</v>
       </c>
       <c r="P71">
-        <v>75.17708385750001</v>
+        <v>74.91178072500001</v>
       </c>
       <c r="Q71">
-        <v>101.7770838575</v>
+        <v>101.511780725</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1748007272243515</v>
+        <v>0.178607013984063</v>
       </c>
       <c r="T71">
-        <v>1.995600223013182</v>
+        <v>2.054482268641671</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.106709725549591</v>
+        <v>5.033756729470311</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0808726541952189</v>
+        <v>0.08065639795088886</v>
       </c>
       <c r="C72">
-        <v>247.8146623336606</v>
+        <v>242.208244924654</v>
       </c>
       <c r="D72">
-        <v>534.6646623336607</v>
+        <v>535.8632449246541</v>
       </c>
       <c r="E72">
-        <v>-35.04999999999995</v>
+        <v>-28.24499999999995</v>
       </c>
       <c r="F72">
-        <v>476.35</v>
+        <v>483.155</v>
       </c>
       <c r="G72">
         <v>189.5</v>
@@ -7179,28 +7179,28 @@
         <v>132.6</v>
       </c>
       <c r="M72">
-        <v>26.342155</v>
+        <v>26.7184715</v>
       </c>
       <c r="N72">
-        <v>106.257845</v>
+        <v>105.8815285</v>
       </c>
       <c r="O72">
-        <v>31.346064275</v>
+        <v>31.2350509075</v>
       </c>
       <c r="P72">
-        <v>74.91178072500001</v>
+        <v>74.64647759250002</v>
       </c>
       <c r="Q72">
-        <v>101.511780725</v>
+        <v>101.2464775925</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.178607013984063</v>
+        <v>0.1826758032789271</v>
       </c>
       <c r="T72">
-        <v>2.054482268641671</v>
+        <v>2.117425145003159</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.033756729470311</v>
+        <v>4.962858747365095</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08065639795088887</v>
+        <v>0.0804401417065588</v>
       </c>
       <c r="C73">
-        <v>242.2082449246541</v>
+        <v>236.6072134259501</v>
       </c>
       <c r="D73">
-        <v>535.8632449246541</v>
+        <v>537.0672134259501</v>
       </c>
       <c r="E73">
-        <v>-28.245</v>
+        <v>-21.44</v>
       </c>
       <c r="F73">
-        <v>483.155</v>
+        <v>489.96</v>
       </c>
       <c r="G73">
         <v>189.5</v>
@@ -7261,28 +7261,28 @@
         <v>132.6</v>
       </c>
       <c r="M73">
-        <v>26.7184715</v>
+        <v>27.094788</v>
       </c>
       <c r="N73">
-        <v>105.8815285</v>
+        <v>105.505212</v>
       </c>
       <c r="O73">
-        <v>31.23505090750001</v>
+        <v>31.12403754000001</v>
       </c>
       <c r="P73">
-        <v>74.64647759250002</v>
+        <v>74.38117446000003</v>
       </c>
       <c r="Q73">
-        <v>101.2464775925</v>
+        <v>100.98117446</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1826758032789271</v>
+        <v>0.1870352203805672</v>
       </c>
       <c r="T73">
-        <v>2.117425145003159</v>
+        <v>2.184863941104753</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.962858747365097</v>
+        <v>4.893930153651691</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0804401417065588</v>
+        <v>0.08022388546222875</v>
       </c>
       <c r="C74">
-        <v>236.6072134259501</v>
+        <v>231.0116042222143</v>
       </c>
       <c r="D74">
-        <v>537.0672134259501</v>
+        <v>538.2766042222142</v>
       </c>
       <c r="E74">
-        <v>-21.44</v>
+        <v>-14.63499999999999</v>
       </c>
       <c r="F74">
-        <v>489.96</v>
+        <v>496.765</v>
       </c>
       <c r="G74">
         <v>189.5</v>
@@ -7343,28 +7343,28 @@
         <v>132.6</v>
       </c>
       <c r="M74">
-        <v>27.094788</v>
+        <v>27.4711045</v>
       </c>
       <c r="N74">
-        <v>105.505212</v>
+        <v>105.1288955</v>
       </c>
       <c r="O74">
-        <v>31.12403754000001</v>
+        <v>31.01302417250001</v>
       </c>
       <c r="P74">
-        <v>74.38117446000003</v>
+        <v>74.11587132750002</v>
       </c>
       <c r="Q74">
-        <v>100.98117446</v>
+        <v>100.7158713275</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1870352203805672</v>
+        <v>0.1917175572675139</v>
       </c>
       <c r="T74">
-        <v>2.184863941104753</v>
+        <v>2.257298203584242</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.893930153651691</v>
+        <v>4.826890014560574</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08022388546222875</v>
+        <v>0.08000762921789871</v>
       </c>
       <c r="C75">
-        <v>231.0116042222143</v>
+        <v>225.421454026582</v>
       </c>
       <c r="D75">
-        <v>538.2766042222142</v>
+        <v>539.491454026582</v>
       </c>
       <c r="E75">
-        <v>-14.63499999999999</v>
+        <v>-7.829999999999984</v>
       </c>
       <c r="F75">
-        <v>496.765</v>
+        <v>503.57</v>
       </c>
       <c r="G75">
         <v>189.5</v>
@@ -7425,28 +7425,28 @@
         <v>132.6</v>
       </c>
       <c r="M75">
-        <v>27.4711045</v>
+        <v>27.847421</v>
       </c>
       <c r="N75">
-        <v>105.1288955</v>
+        <v>104.752579</v>
       </c>
       <c r="O75">
-        <v>31.01302417250001</v>
+        <v>30.90201080500001</v>
       </c>
       <c r="P75">
-        <v>74.11587132750002</v>
+        <v>73.85056819500002</v>
       </c>
       <c r="Q75">
-        <v>100.7158713275</v>
+        <v>100.450568195</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1917175572675139</v>
+        <v>0.196760073914995</v>
       </c>
       <c r="T75">
-        <v>2.257298203584242</v>
+        <v>2.335304332408309</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.826890014560574</v>
+        <v>4.761661771120565</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08000762921789871</v>
+        <v>0.07979137297356866</v>
       </c>
       <c r="C76">
-        <v>225.421454026582</v>
+        <v>219.8367998843739</v>
       </c>
       <c r="D76">
-        <v>539.491454026582</v>
+        <v>540.7117998843739</v>
       </c>
       <c r="E76">
-        <v>-7.829999999999984</v>
+        <v>-1.024999999999977</v>
       </c>
       <c r="F76">
-        <v>503.57</v>
+        <v>510.375</v>
       </c>
       <c r="G76">
         <v>189.5</v>
@@ -7507,28 +7507,28 @@
         <v>132.6</v>
       </c>
       <c r="M76">
-        <v>27.847421</v>
+        <v>28.2237375</v>
       </c>
       <c r="N76">
-        <v>104.752579</v>
+        <v>104.3762625</v>
       </c>
       <c r="O76">
-        <v>30.90201080500001</v>
+        <v>30.79099743750001</v>
       </c>
       <c r="P76">
-        <v>73.85056819500002</v>
+        <v>73.58526506250001</v>
       </c>
       <c r="Q76">
-        <v>100.450568195</v>
+        <v>100.1852650625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.196760073914995</v>
+        <v>0.2022059918942746</v>
       </c>
       <c r="T76">
-        <v>2.335304332408309</v>
+        <v>2.4195509515383</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.761661771120565</v>
+        <v>4.698172947505624</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07979137297356866</v>
+        <v>0.0795751167292386</v>
       </c>
       <c r="C77">
-        <v>219.8367998843739</v>
+        <v>214.257679176861</v>
       </c>
       <c r="D77">
-        <v>540.7117998843739</v>
+        <v>541.9376791768609</v>
       </c>
       <c r="E77">
-        <v>-1.024999999999977</v>
+        <v>5.779999999999973</v>
       </c>
       <c r="F77">
-        <v>510.375</v>
+        <v>517.1799999999999</v>
       </c>
       <c r="G77">
         <v>189.5</v>
@@ -7589,28 +7589,28 @@
         <v>132.6</v>
       </c>
       <c r="M77">
-        <v>28.2237375</v>
+        <v>28.600054</v>
       </c>
       <c r="N77">
-        <v>104.3762625</v>
+        <v>103.999946</v>
       </c>
       <c r="O77">
-        <v>30.79099743750001</v>
+        <v>30.67998407000001</v>
       </c>
       <c r="P77">
-        <v>73.58526506250001</v>
+        <v>73.31996193000002</v>
       </c>
       <c r="Q77">
-        <v>100.1852650625</v>
+        <v>99.91996193000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2022059918942746</v>
+        <v>0.2081057363718275</v>
       </c>
       <c r="T77">
-        <v>2.4195509515383</v>
+        <v>2.510818122262457</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.698172947505624</v>
+        <v>4.636354882406867</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0795751167292386</v>
+        <v>0.07935886048490855</v>
       </c>
       <c r="C78">
-        <v>214.257679176861</v>
+        <v>208.6841296250811</v>
       </c>
       <c r="D78">
-        <v>541.9376791768609</v>
+        <v>543.1691296250812</v>
       </c>
       <c r="E78">
-        <v>5.779999999999973</v>
+        <v>12.58500000000004</v>
       </c>
       <c r="F78">
-        <v>517.1799999999999</v>
+        <v>523.985</v>
       </c>
       <c r="G78">
         <v>189.5</v>
@@ -7671,28 +7671,28 @@
         <v>132.6</v>
       </c>
       <c r="M78">
-        <v>28.600054</v>
+        <v>28.9763705</v>
       </c>
       <c r="N78">
-        <v>103.999946</v>
+        <v>103.6236295</v>
       </c>
       <c r="O78">
-        <v>30.67998407000001</v>
+        <v>30.5689707025</v>
       </c>
       <c r="P78">
-        <v>73.31996193000002</v>
+        <v>73.05465879750003</v>
       </c>
       <c r="Q78">
-        <v>99.91996193000003</v>
+        <v>99.65465879750003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2081057363718275</v>
+        <v>0.214518502108298</v>
       </c>
       <c r="T78">
-        <v>2.510818122262457</v>
+        <v>2.610021568701759</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.636354882406867</v>
+        <v>4.576142481336647</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07935886048490855</v>
+        <v>0.07914260424057851</v>
       </c>
       <c r="C79">
-        <v>208.6841296250811</v>
+        <v>203.1161892937091</v>
       </c>
       <c r="D79">
-        <v>543.1691296250812</v>
+        <v>544.4061892937091</v>
       </c>
       <c r="E79">
-        <v>12.58500000000004</v>
+        <v>19.38999999999999</v>
       </c>
       <c r="F79">
-        <v>523.985</v>
+        <v>530.79</v>
       </c>
       <c r="G79">
         <v>189.5</v>
@@ -7753,28 +7753,28 @@
         <v>132.6</v>
       </c>
       <c r="M79">
-        <v>28.9763705</v>
+        <v>29.352687</v>
       </c>
       <c r="N79">
-        <v>103.6236295</v>
+        <v>103.247313</v>
       </c>
       <c r="O79">
-        <v>30.5689707025</v>
+        <v>30.457957335</v>
       </c>
       <c r="P79">
-        <v>73.05465879750003</v>
+        <v>72.78935566500002</v>
       </c>
       <c r="Q79">
-        <v>99.65465879750003</v>
+        <v>99.38935566500002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.214518502108298</v>
+        <v>0.2215142465480841</v>
       </c>
       <c r="T79">
-        <v>2.610021568701759</v>
+        <v>2.718243510271906</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.576142481336647</v>
+        <v>4.517473987986177</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07914260424057851</v>
+        <v>0.08031872299624845</v>
       </c>
       <c r="C80">
-        <v>203.1161892937091</v>
+        <v>189.6505651791905</v>
       </c>
       <c r="D80">
-        <v>544.4061892937091</v>
+        <v>537.7455651791905</v>
       </c>
       <c r="E80">
-        <v>19.38999999999999</v>
+        <v>26.19500000000005</v>
       </c>
       <c r="F80">
-        <v>530.79</v>
+        <v>537.595</v>
       </c>
       <c r="G80">
         <v>189.5</v>
@@ -7835,45 +7835,45 @@
         <v>132.6</v>
       </c>
       <c r="M80">
-        <v>29.352687</v>
+        <v>31.07299100000001</v>
       </c>
       <c r="N80">
-        <v>103.247313</v>
+        <v>101.527009</v>
       </c>
       <c r="O80">
-        <v>30.457957335</v>
+        <v>29.950467655</v>
       </c>
       <c r="P80">
-        <v>72.78935566500002</v>
+        <v>71.57654134500001</v>
       </c>
       <c r="Q80">
-        <v>99.38935566500002</v>
+        <v>98.17654134500002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2215142465480841</v>
+        <v>0.2291762523630879</v>
       </c>
       <c r="T80">
-        <v>2.718243510271906</v>
+        <v>2.836772303420163</v>
       </c>
       <c r="U80">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V80">
         <v>0.295</v>
       </c>
       <c r="W80">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.517473987986177</v>
+        <v>4.267371621869295</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08031872299624845</v>
+        <v>0.08012009175191839</v>
       </c>
       <c r="C81">
-        <v>189.6505651791905</v>
+        <v>183.9589964050373</v>
       </c>
       <c r="D81">
-        <v>537.7455651791905</v>
+        <v>538.8589964050373</v>
       </c>
       <c r="E81">
-        <v>26.19500000000005</v>
+        <v>33</v>
       </c>
       <c r="F81">
-        <v>537.595</v>
+        <v>544.4</v>
       </c>
       <c r="G81">
         <v>189.5</v>
@@ -7917,28 +7917,28 @@
         <v>132.6</v>
       </c>
       <c r="M81">
-        <v>31.07299100000001</v>
+        <v>31.46632</v>
       </c>
       <c r="N81">
-        <v>101.527009</v>
+        <v>101.13368</v>
       </c>
       <c r="O81">
-        <v>29.950467655</v>
+        <v>29.83443560000001</v>
       </c>
       <c r="P81">
-        <v>71.57654134500001</v>
+        <v>71.29924440000002</v>
       </c>
       <c r="Q81">
-        <v>98.17654134500002</v>
+        <v>97.89924440000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2291762523630879</v>
+        <v>0.237604458759592</v>
       </c>
       <c r="T81">
-        <v>2.836772303420163</v>
+        <v>2.967153975883245</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.267371621869295</v>
+        <v>4.214029476595929</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08012009175191839</v>
+        <v>0.07992146050758833</v>
       </c>
       <c r="C82">
-        <v>183.9589964050373</v>
+        <v>178.2720480366193</v>
       </c>
       <c r="D82">
-        <v>538.8589964050373</v>
+        <v>539.9770480366193</v>
       </c>
       <c r="E82">
-        <v>33</v>
+        <v>39.80500000000006</v>
       </c>
       <c r="F82">
-        <v>544.4</v>
+        <v>551.205</v>
       </c>
       <c r="G82">
         <v>189.5</v>
@@ -7999,28 +7999,28 @@
         <v>132.6</v>
       </c>
       <c r="M82">
-        <v>31.46632</v>
+        <v>31.859649</v>
       </c>
       <c r="N82">
-        <v>101.13368</v>
+        <v>100.740351</v>
       </c>
       <c r="O82">
-        <v>29.83443560000001</v>
+        <v>29.718403545</v>
       </c>
       <c r="P82">
-        <v>71.29924440000002</v>
+        <v>71.02194745500002</v>
       </c>
       <c r="Q82">
-        <v>97.89924440000003</v>
+        <v>97.62194745500003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.237604458759592</v>
+        <v>0.2469198447767808</v>
       </c>
       <c r="T82">
-        <v>2.967153975883245</v>
+        <v>3.111260034921388</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.214029476595929</v>
+        <v>4.162004421329312</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07992146050758833</v>
+        <v>0.07972282926325829</v>
       </c>
       <c r="C83">
-        <v>178.2720480366193</v>
+        <v>172.5897488936805</v>
       </c>
       <c r="D83">
-        <v>539.9770480366193</v>
+        <v>541.0997488936805</v>
       </c>
       <c r="E83">
-        <v>39.80500000000006</v>
+        <v>46.61000000000001</v>
       </c>
       <c r="F83">
-        <v>551.205</v>
+        <v>558.01</v>
       </c>
       <c r="G83">
         <v>189.5</v>
@@ -8081,28 +8081,28 @@
         <v>132.6</v>
       </c>
       <c r="M83">
-        <v>31.859649</v>
+        <v>32.252978</v>
       </c>
       <c r="N83">
-        <v>100.740351</v>
+        <v>100.347022</v>
       </c>
       <c r="O83">
-        <v>29.718403545</v>
+        <v>29.60237149000001</v>
       </c>
       <c r="P83">
-        <v>71.02194745500002</v>
+        <v>70.74465051000001</v>
       </c>
       <c r="Q83">
-        <v>97.62194745500003</v>
+        <v>97.34465051000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2469198447767808</v>
+        <v>0.2572702736847683</v>
       </c>
       <c r="T83">
-        <v>3.111260034921388</v>
+        <v>3.271377878297103</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.162004421329312</v>
+        <v>4.111248269849687</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07972282926325829</v>
+        <v>0.07952419801892824</v>
       </c>
       <c r="C84">
-        <v>172.5897488936805</v>
+        <v>166.9121280361487</v>
       </c>
       <c r="D84">
-        <v>541.0997488936805</v>
+        <v>542.2271280361488</v>
       </c>
       <c r="E84">
-        <v>46.61000000000001</v>
+        <v>53.41500000000008</v>
       </c>
       <c r="F84">
-        <v>558.01</v>
+        <v>564.8150000000001</v>
       </c>
       <c r="G84">
         <v>189.5</v>
@@ -8163,28 +8163,28 @@
         <v>132.6</v>
       </c>
       <c r="M84">
-        <v>32.252978</v>
+        <v>32.64630700000001</v>
       </c>
       <c r="N84">
-        <v>100.347022</v>
+        <v>99.95369300000002</v>
       </c>
       <c r="O84">
-        <v>29.60237149000001</v>
+        <v>29.486339435</v>
       </c>
       <c r="P84">
-        <v>70.74465051000001</v>
+        <v>70.46735356500001</v>
       </c>
       <c r="Q84">
-        <v>97.34465051000002</v>
+        <v>97.06735356500002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2572702736847683</v>
+        <v>0.2688384001113426</v>
       </c>
       <c r="T84">
-        <v>3.271377878297103</v>
+        <v>3.450333115011138</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.111248269849687</v>
+        <v>4.06171515816475</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07952419801892824</v>
+        <v>0.07932556677459819</v>
       </c>
       <c r="C85">
-        <v>166.9121280361487</v>
+        <v>161.239214766642</v>
       </c>
       <c r="D85">
-        <v>542.2271280361488</v>
+        <v>543.359214766642</v>
       </c>
       <c r="E85">
-        <v>53.41500000000008</v>
+        <v>60.22000000000003</v>
       </c>
       <c r="F85">
-        <v>564.8150000000001</v>
+        <v>571.62</v>
       </c>
       <c r="G85">
         <v>189.5</v>
@@ -8245,28 +8245,28 @@
         <v>132.6</v>
       </c>
       <c r="M85">
-        <v>32.64630700000001</v>
+        <v>33.039636</v>
       </c>
       <c r="N85">
-        <v>99.95369300000002</v>
+        <v>99.56036400000002</v>
       </c>
       <c r="O85">
-        <v>29.486339435</v>
+        <v>29.37030738</v>
       </c>
       <c r="P85">
-        <v>70.46735356500001</v>
+        <v>70.19005662000002</v>
       </c>
       <c r="Q85">
-        <v>97.06735356500002</v>
+        <v>96.79005662000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2688384001113426</v>
+        <v>0.2818525423412388</v>
       </c>
       <c r="T85">
-        <v>3.450333115011138</v>
+        <v>3.651657756314427</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.06171515816475</v>
+        <v>4.013361406281837</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07932556677459819</v>
+        <v>0.08122431053026814</v>
       </c>
       <c r="C86">
-        <v>161.239214766642</v>
+        <v>143.8020426919595</v>
       </c>
       <c r="D86">
-        <v>543.359214766642</v>
+        <v>532.7270426919595</v>
       </c>
       <c r="E86">
-        <v>60.22000000000003</v>
+        <v>67.02499999999998</v>
       </c>
       <c r="F86">
-        <v>571.62</v>
+        <v>578.425</v>
       </c>
       <c r="G86">
         <v>189.5</v>
@@ -8327,45 +8327,45 @@
         <v>132.6</v>
       </c>
       <c r="M86">
-        <v>33.039636</v>
+        <v>35.4574525</v>
       </c>
       <c r="N86">
-        <v>99.56036400000002</v>
+        <v>97.14254750000003</v>
       </c>
       <c r="O86">
-        <v>29.37030738</v>
+        <v>28.65705151250001</v>
       </c>
       <c r="P86">
-        <v>70.19005662000002</v>
+        <v>68.48549598750003</v>
       </c>
       <c r="Q86">
-        <v>96.79005662000003</v>
+        <v>95.08549598750004</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2818525423412386</v>
+        <v>0.2966019035351209</v>
       </c>
       <c r="T86">
-        <v>3.651657756314425</v>
+        <v>3.879825683124818</v>
       </c>
       <c r="U86">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V86">
         <v>0.295</v>
       </c>
       <c r="W86">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>4.013361406281837</v>
+        <v>3.739693369116127</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08122431053026814</v>
+        <v>0.08105035428593808</v>
       </c>
       <c r="C87">
-        <v>143.8020426919595</v>
+        <v>137.953779819861</v>
       </c>
       <c r="D87">
-        <v>532.7270426919595</v>
+        <v>533.683779819861</v>
       </c>
       <c r="E87">
-        <v>67.02499999999998</v>
+        <v>73.83000000000004</v>
       </c>
       <c r="F87">
-        <v>578.425</v>
+        <v>585.23</v>
       </c>
       <c r="G87">
         <v>189.5</v>
@@ -8409,28 +8409,28 @@
         <v>132.6</v>
       </c>
       <c r="M87">
-        <v>35.4574525</v>
+        <v>35.874599</v>
       </c>
       <c r="N87">
-        <v>97.14254750000003</v>
+        <v>96.72540100000002</v>
       </c>
       <c r="O87">
-        <v>28.65705151250001</v>
+        <v>28.53399329500001</v>
       </c>
       <c r="P87">
-        <v>68.48549598750003</v>
+        <v>68.19140770500002</v>
       </c>
       <c r="Q87">
-        <v>95.08549598750004</v>
+        <v>94.79140770500003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2966019035351209</v>
+        <v>0.3134583163281291</v>
       </c>
       <c r="T87">
-        <v>3.879825683124818</v>
+        <v>4.140589028050982</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.739693369116127</v>
+        <v>3.696208562498497</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08105035428593808</v>
+        <v>0.08087639804160804</v>
       </c>
       <c r="C88">
-        <v>137.953779819861</v>
+        <v>132.1089595842631</v>
       </c>
       <c r="D88">
-        <v>533.683779819861</v>
+        <v>534.643959584263</v>
       </c>
       <c r="E88">
-        <v>73.83000000000004</v>
+        <v>80.63499999999999</v>
       </c>
       <c r="F88">
-        <v>585.23</v>
+        <v>592.035</v>
       </c>
       <c r="G88">
         <v>189.5</v>
@@ -8491,28 +8491,28 @@
         <v>132.6</v>
       </c>
       <c r="M88">
-        <v>35.874599</v>
+        <v>36.2917455</v>
       </c>
       <c r="N88">
-        <v>96.72540100000002</v>
+        <v>96.30825450000003</v>
       </c>
       <c r="O88">
-        <v>28.53399329500001</v>
+        <v>28.41093507750001</v>
       </c>
       <c r="P88">
-        <v>68.19140770500002</v>
+        <v>67.89731942250003</v>
       </c>
       <c r="Q88">
-        <v>94.79140770500003</v>
+        <v>94.49731942250004</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3134583163281291</v>
+        <v>0.3329080233969848</v>
       </c>
       <c r="T88">
-        <v>4.140589028050982</v>
+        <v>4.441469810658094</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.696208562498497</v>
+        <v>3.65372340660771</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08087639804160804</v>
+        <v>0.08070244179727798</v>
       </c>
       <c r="C89">
-        <v>132.1089595842631</v>
+        <v>126.2676006001655</v>
       </c>
       <c r="D89">
-        <v>534.643959584263</v>
+        <v>535.6076006001655</v>
       </c>
       <c r="E89">
-        <v>80.63499999999999</v>
+        <v>87.44000000000005</v>
       </c>
       <c r="F89">
-        <v>592.035</v>
+        <v>598.84</v>
       </c>
       <c r="G89">
         <v>189.5</v>
@@ -8573,28 +8573,28 @@
         <v>132.6</v>
       </c>
       <c r="M89">
-        <v>36.2917455</v>
+        <v>36.708892</v>
       </c>
       <c r="N89">
-        <v>96.30825450000003</v>
+        <v>95.89110800000003</v>
       </c>
       <c r="O89">
-        <v>28.41093507750001</v>
+        <v>28.28787686000001</v>
       </c>
       <c r="P89">
-        <v>67.89731942250003</v>
+        <v>67.60323114000002</v>
       </c>
       <c r="Q89">
-        <v>94.49731942250004</v>
+        <v>94.20323114000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3329080233969848</v>
+        <v>0.3555993483106498</v>
       </c>
       <c r="T89">
-        <v>4.441469810658094</v>
+        <v>4.792497390366393</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.65372340660771</v>
+        <v>3.612203822441713</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08070244179727798</v>
+        <v>0.08052848555294793</v>
       </c>
       <c r="C90">
-        <v>126.2676006001655</v>
+        <v>120.4297216170166</v>
       </c>
       <c r="D90">
-        <v>535.6076006001655</v>
+        <v>536.5747216170166</v>
       </c>
       <c r="E90">
-        <v>87.44000000000005</v>
+        <v>94.245</v>
       </c>
       <c r="F90">
-        <v>598.84</v>
+        <v>605.645</v>
       </c>
       <c r="G90">
         <v>189.5</v>
@@ -8655,28 +8655,28 @@
         <v>132.6</v>
       </c>
       <c r="M90">
-        <v>36.708892</v>
+        <v>37.1260385</v>
       </c>
       <c r="N90">
-        <v>95.89110800000003</v>
+        <v>95.47396150000003</v>
       </c>
       <c r="O90">
-        <v>28.28787686000001</v>
+        <v>28.16481864250001</v>
       </c>
       <c r="P90">
-        <v>67.60323114000002</v>
+        <v>67.30914285750002</v>
       </c>
       <c r="Q90">
-        <v>94.20323114000003</v>
+        <v>93.90914285750003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3555993483106498</v>
+        <v>0.382416368663163</v>
       </c>
       <c r="T90">
-        <v>4.792497390366393</v>
+        <v>5.20734816638529</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.612203822441713</v>
+        <v>3.571617262638997</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08052848555294793</v>
+        <v>0.08035452930861789</v>
       </c>
       <c r="C91">
-        <v>120.4297216170166</v>
+        <v>114.5953415199303</v>
       </c>
       <c r="D91">
-        <v>536.5747216170166</v>
+        <v>537.5453415199304</v>
       </c>
       <c r="E91">
-        <v>94.245</v>
+        <v>101.0500000000001</v>
       </c>
       <c r="F91">
-        <v>605.645</v>
+        <v>612.45</v>
       </c>
       <c r="G91">
         <v>189.5</v>
@@ -8737,28 +8737,28 @@
         <v>132.6</v>
       </c>
       <c r="M91">
-        <v>37.1260385</v>
+        <v>37.543185</v>
       </c>
       <c r="N91">
-        <v>95.47396150000003</v>
+        <v>95.05681500000003</v>
       </c>
       <c r="O91">
-        <v>28.16481864250001</v>
+        <v>28.04176042500001</v>
       </c>
       <c r="P91">
-        <v>67.30914285750002</v>
+        <v>67.01505457500002</v>
       </c>
       <c r="Q91">
-        <v>93.90914285750003</v>
+        <v>93.61505457500003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.382416368663163</v>
+        <v>0.4145967930861788</v>
       </c>
       <c r="T91">
-        <v>5.20734816638529</v>
+        <v>5.705169097607967</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.571617262638997</v>
+        <v>3.531932626387453</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08035452930861789</v>
+        <v>0.08197691306428784</v>
       </c>
       <c r="C92">
-        <v>114.5953415199303</v>
+        <v>98.87204458988151</v>
       </c>
       <c r="D92">
-        <v>537.5453415199304</v>
+        <v>528.6270445898815</v>
       </c>
       <c r="E92">
-        <v>101.0500000000001</v>
+        <v>107.855</v>
       </c>
       <c r="F92">
-        <v>612.45</v>
+        <v>619.255</v>
       </c>
       <c r="G92">
         <v>189.5</v>
@@ -8819,45 +8819,45 @@
         <v>132.6</v>
       </c>
       <c r="M92">
-        <v>37.543185</v>
+        <v>39.6942455</v>
       </c>
       <c r="N92">
-        <v>95.05681500000003</v>
+        <v>92.90575450000003</v>
       </c>
       <c r="O92">
-        <v>28.04176042500001</v>
+        <v>27.40719757750001</v>
       </c>
       <c r="P92">
-        <v>67.01505457500002</v>
+        <v>65.49855692250003</v>
       </c>
       <c r="Q92">
-        <v>93.61505457500003</v>
+        <v>92.09855692250004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4145967930861788</v>
+        <v>0.4539284229365316</v>
       </c>
       <c r="T92">
-        <v>5.705169097607967</v>
+        <v>6.313616902435685</v>
       </c>
       <c r="U92">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V92">
         <v>0.295</v>
       </c>
       <c r="W92">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y92">
-        <v>3.531932626387453</v>
+        <v>3.340534587059981</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08197691306428784</v>
+        <v>0.08182269681995777</v>
       </c>
       <c r="C93">
-        <v>98.87204458988151</v>
+        <v>92.90202863649029</v>
       </c>
       <c r="D93">
-        <v>528.6270445898815</v>
+        <v>529.4620286364903</v>
       </c>
       <c r="E93">
-        <v>107.855</v>
+        <v>114.6600000000001</v>
       </c>
       <c r="F93">
-        <v>619.255</v>
+        <v>626.0600000000001</v>
       </c>
       <c r="G93">
         <v>189.5</v>
@@ -8901,28 +8901,28 @@
         <v>132.6</v>
       </c>
       <c r="M93">
-        <v>39.6942455</v>
+        <v>40.13044600000001</v>
       </c>
       <c r="N93">
-        <v>92.90575450000003</v>
+        <v>92.46955400000002</v>
       </c>
       <c r="O93">
-        <v>27.40719757750001</v>
+        <v>27.27851843</v>
       </c>
       <c r="P93">
-        <v>65.49855692250003</v>
+        <v>65.19103557000001</v>
       </c>
       <c r="Q93">
-        <v>92.09855692250004</v>
+        <v>91.79103557000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4539284229365316</v>
+        <v>0.5030929602494724</v>
       </c>
       <c r="T93">
-        <v>6.313616902435685</v>
+        <v>7.07417665847033</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.340534587059981</v>
+        <v>3.304224428504981</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08182269681995777</v>
+        <v>0.08166848057562773</v>
       </c>
       <c r="C94">
-        <v>92.90202863649029</v>
+        <v>86.93465462643314</v>
       </c>
       <c r="D94">
-        <v>529.4620286364903</v>
+        <v>530.2996546264332</v>
       </c>
       <c r="E94">
-        <v>114.6600000000001</v>
+        <v>121.465</v>
       </c>
       <c r="F94">
-        <v>626.0600000000001</v>
+        <v>632.865</v>
       </c>
       <c r="G94">
         <v>189.5</v>
@@ -8983,28 +8983,28 @@
         <v>132.6</v>
       </c>
       <c r="M94">
-        <v>40.13044600000001</v>
+        <v>40.5666465</v>
       </c>
       <c r="N94">
-        <v>92.46955400000002</v>
+        <v>92.03335350000002</v>
       </c>
       <c r="O94">
-        <v>27.27851843</v>
+        <v>27.1498392825</v>
       </c>
       <c r="P94">
-        <v>65.19103557000001</v>
+        <v>64.88351421750002</v>
       </c>
       <c r="Q94">
-        <v>91.79103557000002</v>
+        <v>91.48351421750003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5030929602494724</v>
+        <v>0.5663045082232535</v>
       </c>
       <c r="T94">
-        <v>7.07417665847033</v>
+        <v>8.052039201943447</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.304224428504981</v>
+        <v>3.26869513357482</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08166848057562773</v>
+        <v>0.08151426433129767</v>
       </c>
       <c r="C95">
-        <v>86.93465462643314</v>
+        <v>80.96993511849701</v>
       </c>
       <c r="D95">
-        <v>530.2996546264332</v>
+        <v>531.1399351184971</v>
       </c>
       <c r="E95">
-        <v>121.465</v>
+        <v>128.2700000000001</v>
       </c>
       <c r="F95">
-        <v>632.865</v>
+        <v>639.6700000000001</v>
       </c>
       <c r="G95">
         <v>189.5</v>
@@ -9065,28 +9065,28 @@
         <v>132.6</v>
       </c>
       <c r="M95">
-        <v>40.5666465</v>
+        <v>41.00284700000001</v>
       </c>
       <c r="N95">
-        <v>92.03335350000002</v>
+        <v>91.59715300000002</v>
       </c>
       <c r="O95">
-        <v>27.1498392825</v>
+        <v>27.02116013500001</v>
       </c>
       <c r="P95">
-        <v>64.88351421750002</v>
+        <v>64.57599286500002</v>
       </c>
       <c r="Q95">
-        <v>91.48351421750003</v>
+        <v>91.17599286500003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5663045082232535</v>
+        <v>0.6505865721882951</v>
       </c>
       <c r="T95">
-        <v>8.052039201943447</v>
+        <v>9.355855926574272</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.26869513357482</v>
+        <v>3.233921781089981</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08151426433129767</v>
+        <v>0.08136004808696762</v>
       </c>
       <c r="C96">
-        <v>80.96993511849701</v>
+        <v>75.00788275119476</v>
       </c>
       <c r="D96">
-        <v>531.1399351184971</v>
+        <v>531.9828827511948</v>
       </c>
       <c r="E96">
-        <v>128.2700000000001</v>
+        <v>135.075</v>
       </c>
       <c r="F96">
-        <v>639.6700000000001</v>
+        <v>646.475</v>
       </c>
       <c r="G96">
         <v>189.5</v>
@@ -9147,28 +9147,28 @@
         <v>132.6</v>
       </c>
       <c r="M96">
-        <v>41.00284700000001</v>
+        <v>41.4390475</v>
       </c>
       <c r="N96">
-        <v>91.59715300000002</v>
+        <v>91.16095250000002</v>
       </c>
       <c r="O96">
-        <v>27.02116013500001</v>
+        <v>26.8924809875</v>
       </c>
       <c r="P96">
-        <v>64.57599286500002</v>
+        <v>64.26847151250001</v>
       </c>
       <c r="Q96">
-        <v>91.17599286500003</v>
+        <v>90.86847151250002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6505865721882951</v>
+        <v>0.7685814617393534</v>
       </c>
       <c r="T96">
-        <v>9.355855926574272</v>
+        <v>11.18119934105743</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.233921781089981</v>
+        <v>3.199880499183771</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08136004808696762</v>
+        <v>0.08120583184263758</v>
       </c>
       <c r="C97">
-        <v>75.00788275119476</v>
+        <v>69.04851024339848</v>
       </c>
       <c r="D97">
-        <v>531.9828827511948</v>
+        <v>532.8285102433986</v>
       </c>
       <c r="E97">
-        <v>135.075</v>
+        <v>141.8800000000001</v>
       </c>
       <c r="F97">
-        <v>646.475</v>
+        <v>653.2800000000001</v>
       </c>
       <c r="G97">
         <v>189.5</v>
@@ -9229,28 +9229,28 @@
         <v>132.6</v>
       </c>
       <c r="M97">
-        <v>41.4390475</v>
+        <v>41.87524800000001</v>
       </c>
       <c r="N97">
-        <v>91.16095250000002</v>
+        <v>90.72475200000002</v>
       </c>
       <c r="O97">
-        <v>26.8924809875</v>
+        <v>26.76380184000001</v>
       </c>
       <c r="P97">
-        <v>64.26847151250001</v>
+        <v>63.96095016000002</v>
       </c>
       <c r="Q97">
-        <v>90.86847151250002</v>
+        <v>90.56095016000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7685814617393534</v>
+        <v>0.9455737960659407</v>
       </c>
       <c r="T97">
-        <v>11.18119934105743</v>
+        <v>13.91921446278216</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.199880499183771</v>
+        <v>3.166548410650607</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08120583184263758</v>
+        <v>0.08105161559830754</v>
       </c>
       <c r="C98">
-        <v>69.0485102433986</v>
+        <v>63.09183039497975</v>
       </c>
       <c r="D98">
-        <v>532.8285102433986</v>
+        <v>533.6768303949798</v>
       </c>
       <c r="E98">
-        <v>141.88</v>
+        <v>148.6850000000001</v>
       </c>
       <c r="F98">
-        <v>653.28</v>
+        <v>660.085</v>
       </c>
       <c r="G98">
         <v>189.5</v>
@@ -9311,28 +9311,28 @@
         <v>132.6</v>
       </c>
       <c r="M98">
-        <v>41.875248</v>
+        <v>42.3114485</v>
       </c>
       <c r="N98">
-        <v>90.72475200000002</v>
+        <v>90.28855150000001</v>
       </c>
       <c r="O98">
-        <v>26.76380184000001</v>
+        <v>26.6351226925</v>
       </c>
       <c r="P98">
-        <v>63.96095016000002</v>
+        <v>63.65342880750001</v>
       </c>
       <c r="Q98">
-        <v>90.56095016000003</v>
+        <v>90.25342880750001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9455737960659384</v>
+        <v>1.240561019943583</v>
       </c>
       <c r="T98">
-        <v>13.91921446278212</v>
+        <v>18.48257299898999</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.166548410650607</v>
+        <v>3.133903581674828</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08105161559830754</v>
+        <v>0.08089739935397748</v>
       </c>
       <c r="C99">
-        <v>63.09183039497975</v>
+        <v>57.13785608745525</v>
       </c>
       <c r="D99">
-        <v>533.6768303949798</v>
+        <v>534.5278560874552</v>
       </c>
       <c r="E99">
-        <v>148.6850000000001</v>
+        <v>155.49</v>
       </c>
       <c r="F99">
-        <v>660.085</v>
+        <v>666.89</v>
       </c>
       <c r="G99">
         <v>189.5</v>
@@ -9393,28 +9393,28 @@
         <v>132.6</v>
       </c>
       <c r="M99">
-        <v>42.3114485</v>
+        <v>42.747649</v>
       </c>
       <c r="N99">
-        <v>90.28855150000001</v>
+        <v>89.85235100000003</v>
       </c>
       <c r="O99">
-        <v>26.6351226925</v>
+        <v>26.50644354500001</v>
       </c>
       <c r="P99">
-        <v>63.65342880750001</v>
+        <v>63.34590745500002</v>
       </c>
       <c r="Q99">
-        <v>90.25342880750001</v>
+        <v>89.94590745500003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.240561019943583</v>
+        <v>1.830535467698872</v>
       </c>
       <c r="T99">
-        <v>18.48257299898999</v>
+        <v>27.60929007140572</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.133903581674828</v>
+        <v>3.101924973698554</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08089739935397748</v>
+        <v>0.08074318310964743</v>
       </c>
       <c r="C100">
-        <v>57.13785608745525</v>
+        <v>51.18660028463853</v>
       </c>
       <c r="D100">
-        <v>534.5278560874552</v>
+        <v>535.3816002846386</v>
       </c>
       <c r="E100">
-        <v>155.49</v>
+        <v>162.2950000000001</v>
       </c>
       <c r="F100">
-        <v>666.89</v>
+        <v>673.6950000000001</v>
       </c>
       <c r="G100">
         <v>189.5</v>
@@ -9475,28 +9475,28 @@
         <v>132.6</v>
       </c>
       <c r="M100">
-        <v>42.747649</v>
+        <v>43.18384950000001</v>
       </c>
       <c r="N100">
-        <v>89.85235100000003</v>
+        <v>89.41615050000001</v>
       </c>
       <c r="O100">
-        <v>26.50644354500001</v>
+        <v>26.3777643975</v>
       </c>
       <c r="P100">
-        <v>63.34590745500002</v>
+        <v>63.03838610250001</v>
       </c>
       <c r="Q100">
-        <v>89.94590745500003</v>
+        <v>89.63838610250002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.830535467698872</v>
+        <v>3.600458810964738</v>
       </c>
       <c r="T100">
-        <v>27.60929007140572</v>
+        <v>54.98944128865291</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.101924973698554</v>
+        <v>3.070592398206649</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08074318310964743</v>
-      </c>
-      <c r="C101">
-        <v>51.18660028463853</v>
-      </c>
-      <c r="D101">
-        <v>535.3816002846386</v>
-      </c>
-      <c r="E101">
-        <v>162.2950000000001</v>
-      </c>
-      <c r="F101">
-        <v>673.6950000000001</v>
-      </c>
-      <c r="G101">
-        <v>189.5</v>
-      </c>
-      <c r="H101">
-        <v>169.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>159.2</v>
-      </c>
-      <c r="K101">
-        <v>26.60000000000001</v>
-      </c>
-      <c r="L101">
-        <v>132.6</v>
-      </c>
-      <c r="M101">
-        <v>43.18384950000001</v>
-      </c>
-      <c r="N101">
-        <v>89.41615050000001</v>
-      </c>
-      <c r="O101">
-        <v>26.3777643975</v>
-      </c>
-      <c r="P101">
-        <v>63.03838610250001</v>
-      </c>
-      <c r="Q101">
-        <v>89.63838610250002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.600458810964738</v>
-      </c>
-      <c r="T101">
-        <v>54.98944128865291</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.295</v>
-      </c>
-      <c r="W101">
-        <v>0.04519050000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.070592398206649</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
